--- a/data/Czech/KCOR_summary.xlsx
+++ b/data/Czech/KCOR_summary.xlsx
@@ -493,17 +493,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.3097</t>
+          <t>1.2730</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.281</t>
+          <t>1.245</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.339</t>
+          <t>1.302</t>
         </is>
       </c>
     </row>
@@ -516,17 +516,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.9837</t>
+          <t>0.9372</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>1.021</t>
         </is>
       </c>
     </row>
@@ -539,17 +539,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.0132</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.008</t>
+          <t>0.971</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.099</t>
+          <t>1.057</t>
         </is>
       </c>
     </row>
@@ -562,17 +562,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.5883</t>
+          <t>1.5400</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.539</t>
+          <t>1.492</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.589</t>
         </is>
       </c>
     </row>
@@ -585,17 +585,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.6341</t>
+          <t>1.6034</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.482</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.768</t>
+          <t>1.734</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.4582</t>
+          <t>1.4221</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>1.232</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.683</t>
+          <t>1.641</t>
         </is>
       </c>
     </row>
@@ -631,17 +631,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.0768</t>
+          <t>2.9826</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.415</t>
+          <t>2.341</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.920</t>
+          <t>3.800</t>
         </is>
       </c>
     </row>
@@ -654,17 +654,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.0891</t>
+          <t>1.0472</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>0.691</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.650</t>
+          <t>1.586</t>
         </is>
       </c>
     </row>
@@ -677,17 +677,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.6680</t>
+          <t>2.5682</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.694</t>
+          <t>1.632</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4.203</t>
+          <t>4.041</t>
         </is>
       </c>
     </row>
@@ -700,17 +700,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12.6258</t>
+          <t>12.4845</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5.940</t>
+          <t>5.875</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26.839</t>
+          <t>26.530</t>
         </is>
       </c>
     </row>
@@ -741,17 +741,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.5778</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1.508</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.559</t>
         </is>
       </c>
     </row>
@@ -764,17 +764,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.3491</t>
+          <t>1.2853</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.290</t>
+          <t>1.230</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.411</t>
+          <t>1.343</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.5714</t>
+          <t>1.5126</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.474</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.613</t>
+          <t>1.552</t>
         </is>
       </c>
     </row>
@@ -810,17 +810,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.6561</t>
+          <t>1.6057</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1.545</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.722</t>
+          <t>1.669</t>
         </is>
       </c>
     </row>
@@ -833,17 +833,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.2616</t>
+          <t>1.2380</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.171</t>
+          <t>1.149</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.360</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.2856</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>1.083</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.451</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.1379</t>
+          <t>1.1030</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.895</t>
+          <t>0.868</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.446</t>
+          <t>1.402</t>
         </is>
       </c>
     </row>
@@ -902,17 +902,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.6223</t>
+          <t>0.5983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.961</t>
+          <t>0.924</t>
         </is>
       </c>
     </row>
@@ -925,17 +925,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.2343</t>
+          <t>1.1881</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>0.709</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.991</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2.2733</t>
+          <t>2.2478</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16.215</t>
+          <t>16.031</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.1975</t>
+          <t>1.1573</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>1.135</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1.180</t>
         </is>
       </c>
     </row>
@@ -1312,17 +1312,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7004</t>
+          <t>0.6681</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>0.604</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>0.739</t>
         </is>
       </c>
     </row>
@@ -1335,17 +1335,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.0274</t>
+          <t>0.9813</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.977</t>
+          <t>0.933</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.081</t>
+          <t>1.032</t>
         </is>
       </c>
     </row>
@@ -1358,17 +1358,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.1094</t>
+          <t>1.0733</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.072</t>
+          <t>1.038</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>1.110</t>
         </is>
       </c>
     </row>
@@ -1381,17 +1381,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.5367</t>
+          <t>1.4924</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.442</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.590</t>
+          <t>1.544</t>
         </is>
       </c>
     </row>
@@ -1404,17 +1404,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.4665</t>
+          <t>1.4221</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.379</t>
+          <t>1.338</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.511</t>
         </is>
       </c>
     </row>
@@ -1427,17 +1427,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.2574</t>
+          <t>1.2246</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>1.089</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1.377</t>
         </is>
       </c>
     </row>
@@ -1450,17 +1450,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.2424</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.031</t>
+          <t>0.991</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.558</t>
         </is>
       </c>
     </row>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.1189</t>
+          <t>1.0686</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>0.661</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.811</t>
+          <t>1.728</t>
         </is>
       </c>
     </row>
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12.0943</t>
+          <t>11.9909</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.251</t>
+          <t>8.184</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17.728</t>
+          <t>17.569</t>
         </is>
       </c>
     </row>
@@ -1537,17 +1537,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.1422</t>
+          <t>1.1039</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.126</t>
+          <t>1.089</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>1.120</t>
         </is>
       </c>
     </row>
@@ -1560,17 +1560,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.9643</t>
+          <t>0.9198</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>0.882</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>0.959</t>
         </is>
       </c>
     </row>
@@ -1583,17 +1583,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.0574</t>
+          <t>1.0100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.031</t>
+          <t>0.986</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>1.035</t>
         </is>
       </c>
     </row>
@@ -1606,17 +1606,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.2979</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.224</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.332</t>
+          <t>1.288</t>
         </is>
       </c>
     </row>
@@ -1629,17 +1629,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.1010</t>
+          <t>1.0692</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.047</t>
+          <t>1.017</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>1.124</t>
         </is>
       </c>
     </row>
@@ -1652,17 +1652,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.2918</t>
+          <t>1.2528</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.177</t>
+          <t>1.142</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.418</t>
+          <t>1.375</t>
         </is>
       </c>
     </row>
@@ -1675,17 +1675,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.0577</t>
+          <t>1.0301</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.911</t>
+          <t>0.888</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.228</t>
+          <t>1.195</t>
         </is>
       </c>
     </row>
@@ -1698,17 +1698,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.8176</t>
+          <t>2.7059</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.202</t>
+          <t>2.116</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3.605</t>
+          <t>3.460</t>
         </is>
       </c>
     </row>
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.9244</t>
+          <t>0.8828</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>0.635</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.287</t>
+          <t>1.227</t>
         </is>
       </c>
     </row>
@@ -1744,17 +1744,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7.1546</t>
+          <t>7.0935</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.793</t>
+          <t>3.762</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13.495</t>
+          <t>13.377</t>
         </is>
       </c>
     </row>
@@ -2085,17 +2085,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.9653</t>
+          <t>0.9292</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.944</t>
+          <t>0.909</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.987</t>
+          <t>0.950</t>
         </is>
       </c>
     </row>
@@ -2108,17 +2108,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.6673</t>
+          <t>0.6358</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>0.565</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>0.715</t>
         </is>
       </c>
     </row>
@@ -2131,17 +2131,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.9209</t>
+          <t>0.8751</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>0.828</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>0.924</t>
         </is>
       </c>
     </row>
@@ -2154,17 +2154,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.8833</t>
+          <t>0.8511</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>0.815</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>0.889</t>
         </is>
       </c>
     </row>
@@ -2177,17 +2177,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.1270</t>
+          <t>1.0902</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>1.047</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>1.135</t>
         </is>
       </c>
     </row>
@@ -2200,17 +2200,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.1444</t>
+          <t>1.1077</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>1.045</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.214</t>
+          <t>1.175</t>
         </is>
       </c>
     </row>
@@ -2223,17 +2223,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.2772</t>
+          <t>1.2436</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.168</t>
+          <t>1.138</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.397</t>
+          <t>1.359</t>
         </is>
       </c>
     </row>
@@ -2246,17 +2246,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.9802</t>
+          <t>0.9481</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.823</t>
+          <t>0.797</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.168</t>
+          <t>1.128</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2269,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.3550</t>
+          <t>3.1828</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.392</t>
+          <t>2.274</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4.707</t>
+          <t>4.455</t>
         </is>
       </c>
     </row>
@@ -2292,17 +2292,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.5925</t>
+          <t>0.5841</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>0.300</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.152</t>
+          <t>1.135</t>
         </is>
       </c>
     </row>
@@ -2333,17 +2333,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.0567</t>
+          <t>1.0172</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.043</t>
+          <t>1.004</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.071</t>
+          <t>1.031</t>
         </is>
       </c>
     </row>
@@ -2356,17 +2356,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.8816</t>
+          <t>0.8401</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>0.805</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>0.876</t>
         </is>
       </c>
     </row>
@@ -2379,17 +2379,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.9856</t>
+          <t>0.9366</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.961</t>
+          <t>0.914</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>0.960</t>
         </is>
       </c>
     </row>
@@ -2402,17 +2402,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.0860</t>
+          <t>1.0464</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.060</t>
+          <t>1.022</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.113</t>
+          <t>1.071</t>
         </is>
       </c>
     </row>
@@ -2425,17 +2425,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.3357</t>
+          <t>1.2922</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.291</t>
+          <t>1.249</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.382</t>
+          <t>1.337</t>
         </is>
       </c>
     </row>
@@ -2448,17 +2448,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.0912</t>
+          <t>1.0562</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>0.986</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.169</t>
+          <t>1.131</t>
         </is>
       </c>
     </row>
@@ -2471,17 +2471,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.1486</t>
+          <t>1.1184</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.026</t>
+          <t>0.999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.252</t>
         </is>
       </c>
     </row>
@@ -2494,17 +2494,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.3253</t>
+          <t>1.2819</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>1.048</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.623</t>
+          <t>1.568</t>
         </is>
       </c>
     </row>
@@ -2517,17 +2517,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.2608</t>
+          <t>2.1448</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.683</t>
+          <t>1.600</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.038</t>
+          <t>2.875</t>
         </is>
       </c>
     </row>
@@ -2540,17 +2540,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.3854</t>
+          <t>1.3659</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.968</t>
+          <t>0.955</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.984</t>
+          <t>1.954</t>
         </is>
       </c>
     </row>
@@ -2881,17 +2881,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6494</t>
+          <t>0.6229</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>0.601</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>0.646</t>
         </is>
       </c>
     </row>
@@ -2904,17 +2904,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.4475</t>
+          <t>0.4255</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.537</t>
+          <t>0.511</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.6207</t>
+          <t>0.5884</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>0.542</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>0.638</t>
         </is>
       </c>
     </row>
@@ -2950,17 +2950,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.6032</t>
+          <t>0.5786</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>0.540</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.620</t>
         </is>
       </c>
     </row>
@@ -2973,17 +2973,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.6362</t>
+          <t>0.6146</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.590</t>
+          <t>0.570</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>0.662</t>
         </is>
       </c>
     </row>
@@ -2996,17 +2996,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.9824</t>
+          <t>0.9494</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.880</t>
+          <t>0.850</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.097</t>
+          <t>1.060</t>
         </is>
       </c>
     </row>
@@ -3019,17 +3019,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.0974</t>
+          <t>1.0622</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.947</t>
+          <t>0.917</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1.230</t>
         </is>
       </c>
     </row>
@@ -3042,17 +3042,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.2513</t>
+          <t>1.2058</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>0.990</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1.468</t>
         </is>
       </c>
     </row>
@@ -3065,17 +3065,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.0556</t>
+          <t>1.0090</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.770</t>
+          <t>0.738</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.446</t>
+          <t>1.379</t>
         </is>
       </c>
     </row>
@@ -3088,17 +3088,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.2004</t>
+          <t>1.1597</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>0.789</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.767</t>
+          <t>1.704</t>
         </is>
       </c>
     </row>
@@ -3129,17 +3129,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.9110</t>
+          <t>0.8737</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.900</t>
+          <t>0.863</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>0.885</t>
         </is>
       </c>
     </row>
@@ -3152,17 +3152,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.7837</t>
+          <t>0.7453</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>0.715</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>0.777</t>
         </is>
       </c>
     </row>
@@ -3175,17 +3175,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.8268</t>
+          <t>0.7838</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>0.803</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.9152</t>
+          <t>0.8780</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>0.858</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>0.898</t>
         </is>
       </c>
     </row>
@@ -3221,17 +3221,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.9469</t>
+          <t>0.9147</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>0.888</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.976</t>
+          <t>0.942</t>
         </is>
       </c>
     </row>
@@ -3244,17 +3244,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.3073</t>
+          <t>1.2633</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1.203</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.327</t>
         </is>
       </c>
     </row>
@@ -3267,17 +3267,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.1390</t>
+          <t>1.1025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.054</t>
+          <t>1.022</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.230</t>
+          <t>1.190</t>
         </is>
       </c>
     </row>
@@ -3290,17 +3290,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.6839</t>
+          <t>1.6227</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.460</t>
+          <t>1.410</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.942</t>
+          <t>1.868</t>
         </is>
       </c>
     </row>
@@ -3313,17 +3313,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.1717</t>
+          <t>1.1200</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>0.881</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.424</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.2940</t>
+          <t>0.2840</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.460</t>
+          <t>0.444</t>
         </is>
       </c>
     </row>

--- a/data/Czech/KCOR_summary.xlsx
+++ b/data/Czech/KCOR_summary.xlsx
@@ -827,17 +827,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.0309</t>
+          <t>1.0730</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>0.703</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>99.99836701224508</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>11</v>
@@ -1271,27 +1271,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.6115</t>
+          <t>0.6223</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>0.403</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.932</t>
+          <t>0.961</t>
         </is>
       </c>
       <c r="F23" t="b">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>67.15278858582882</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>99.99836701224508</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>11</v>
@@ -1715,24 +1715,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.5932</t>
+          <t>0.5799</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.070</t>
+          <t>1.056</t>
         </is>
       </c>
       <c r="F35" t="b">
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>67.15278858582882</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2249,24 +2249,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.2015</t>
+          <t>1.1890</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1.513</t>
         </is>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>20.17276949813065</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>59.757586912448</v>
@@ -3137,17 +3137,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2.2885</t>
+          <t>2.3124</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.645</t>
+          <t>1.659</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3.184</t>
+          <t>3.223</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -3157,7 +3157,7 @@
         <v>3.072968489481465e-05</v>
       </c>
       <c r="H35" t="n">
-        <v>20.17276949813065</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>11</v>
@@ -3425,27 +3425,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7458</t>
+          <t>0.7689</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.682</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>0.867</t>
         </is>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.368184590370468</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4381125719082086</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>11</v>
@@ -3671,27 +3671,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.9494</t>
+          <t>0.9988</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.798</t>
+          <t>0.838</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.130</t>
+          <t>1.191</t>
         </is>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.004735882525673585</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>99.99999874596539</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>11</v>
@@ -3712,17 +3712,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.2920</t>
+          <t>3.3550</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.349</t>
+          <t>2.392</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4.614</t>
+          <t>4.707</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -3732,7 +3732,7 @@
         <v>0.0002366379193354806</v>
       </c>
       <c r="H12" t="n">
-        <v>99.98397501305337</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>11</v>
@@ -3869,17 +3869,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.9351</t>
+          <t>1.0158</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>0.969</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -3889,7 +3889,7 @@
         <v>1e-10</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4381125719082086</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>11</v>
@@ -4115,17 +4115,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.2836</t>
+          <t>1.3504</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.049</t>
+          <t>1.102</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.570</t>
+          <t>1.655</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -4135,7 +4135,7 @@
         <v>0.000434689012210665</v>
       </c>
       <c r="H23" t="n">
-        <v>99.99999874596539</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>11</v>
@@ -4156,17 +4156,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.0579</t>
+          <t>2.0973</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.528</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.822</t>
+          <t>2.879</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -4176,7 +4176,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>99.98397501305337</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>11</v>
@@ -4313,17 +4313,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.2538</t>
+          <t>1.3212</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.122</t>
+          <t>1.175</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.401</t>
+          <t>1.486</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -4333,7 +4333,7 @@
         <v>1e-10</v>
       </c>
       <c r="H29" t="n">
-        <v>0.368184590370468</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>11</v>
@@ -4579,7 +4579,7 @@
         <v>0.000434689012210665</v>
       </c>
       <c r="H35" t="n">
-        <v>0.004735882525673585</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>11</v>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.6070</t>
+          <t>0.6624</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>0.575</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>0.763</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -4867,7 +4867,7 @@
         <v>1.387534855497648</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4537941446299353</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
@@ -4929,24 +4929,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.6865</t>
+          <t>0.6087</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>0.565</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>0.655</t>
         </is>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>5.144869335656168</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>2.979749884865235</v>
@@ -4970,24 +4970,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.7166</t>
+          <t>0.6358</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>0.588</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>0.687</t>
         </is>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>12.94399970085989</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>7.652980279154328</v>
@@ -5093,27 +5093,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.1542</t>
+          <t>1.2151</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.940</t>
+          <t>0.986</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>18.07141117982593</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>99.99832749090832</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
@@ -5134,27 +5134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.0486</t>
+          <t>1.0614</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>0.774</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.430</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>99.99883438093936</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>99.99655614702037</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>5</v>
@@ -5175,17 +5175,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.2080</t>
+          <t>1.2225</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.820</t>
+          <t>0.829</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.779</t>
+          <t>1.802</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -5195,7 +5195,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>99.88585064778931</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>5</v>
@@ -5291,17 +5291,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.8453</t>
+          <t>0.9224</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>0.880</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>0.967</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -5311,7 +5311,7 @@
         <v>1e-10</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4537941446299353</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>5</v>
@@ -5537,17 +5537,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.6230</t>
+          <t>1.7184</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.410</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.868</t>
+          <t>1.983</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -5557,7 +5557,7 @@
         <v>0.001600423735280132</v>
       </c>
       <c r="H23" t="n">
-        <v>99.99832749090832</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>5</v>
@@ -5566,7 +5566,7 @@
         <v>5</v>
       </c>
       <c r="K23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -5578,27 +5578,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.1687</t>
+          <t>1.1782</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.920</t>
+          <t>0.923</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.484</t>
+          <t>1.503</t>
         </is>
       </c>
       <c r="F24" t="b">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>73.33347320005834</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>99.99655614702037</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>5</v>
@@ -5619,17 +5619,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.2685</t>
+          <t>0.2717</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.160</t>
+          <t>0.162</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.450</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -5639,7 +5639,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>99.88585064778931</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>5</v>
@@ -5817,17 +5817,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.4057</t>
+          <t>1.5854</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1.706</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -5837,7 +5837,7 @@
         <v>3.023117197968237e-09</v>
       </c>
       <c r="H31" t="n">
-        <v>5.144869335656168</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>5</v>
@@ -5858,17 +5858,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.3639</t>
+          <t>1.5373</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.274</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.662</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -5878,7 +5878,7 @@
         <v>1e-10</v>
       </c>
       <c r="H32" t="n">
-        <v>12.94399970085989</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>5</v>
@@ -5981,17 +5981,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.4061</t>
+          <t>1.4142</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.121</t>
+          <t>1.126</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.764</t>
+          <t>1.776</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -6001,7 +6001,7 @@
         <v>0.001600423735280132</v>
       </c>
       <c r="H35" t="n">
-        <v>18.07141117982593</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>5</v>
@@ -6022,27 +6022,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.1145</t>
+          <t>1.1100</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.785</t>
+          <t>0.777</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F36" t="b">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>73.33347320005834</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>99.99883438093936</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>5</v>
@@ -6269,24 +6269,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.9217</t>
+          <t>0.8713</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>0.657</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>1.155</t>
         </is>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4324265093155894</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>1.483209665604275</v>
@@ -6433,24 +6433,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.8509</t>
+          <t>0.6965</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>0.570</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.997</t>
+          <t>0.851</t>
         </is>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>27.49288398547458</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>30.03019045477097</v>
@@ -6474,27 +6474,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.9792</t>
+          <t>0.9082</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>0.704</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>1.171</t>
         </is>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>78.68485143096366</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>99.99996360706962</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
@@ -6515,17 +6515,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.0126</t>
+          <t>1.0792</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>0.756</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>1.540</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -6535,7 +6535,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>99.99982965062681</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>4</v>
@@ -6556,17 +6556,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.2047</t>
+          <t>1.2431</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>0.726</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.059</t>
+          <t>2.128</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -6576,7 +6576,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>99.99801771045323</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -6597,17 +6597,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.3096</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>0.100</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>0.989</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -6617,7 +6617,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>99.99881055196656</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>4</v>
@@ -6918,27 +6918,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.1300</t>
+          <t>1.2703</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.042</t>
+          <t>1.161</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>1.389</t>
         </is>
       </c>
       <c r="F22" t="b">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>38.52515852264099</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>99.99996360706962</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>4</v>
@@ -6959,17 +6959,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.0514</t>
+          <t>1.1205</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>0.968</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.212</t>
+          <t>1.297</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -6979,7 +6979,7 @@
         <v>0.0002633315537803882</v>
       </c>
       <c r="H23" t="n">
-        <v>99.99982965062681</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
@@ -7000,17 +7000,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.9069</t>
+          <t>1.9621</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.345</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -7020,7 +7020,7 @@
         <v>0.002196355696408192</v>
       </c>
       <c r="H24" t="n">
-        <v>99.99801771045323</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>4</v>
@@ -7041,17 +7041,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.3416</t>
+          <t>1.3618</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.021</t>
+          <t>1.034</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -7061,7 +7061,7 @@
         <v>0.002465793332856014</v>
       </c>
       <c r="H25" t="n">
-        <v>99.99881055196656</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>4</v>
@@ -7362,17 +7362,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.3039</t>
+          <t>1.5192</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.198</t>
+          <t>1.387</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.419</t>
+          <t>1.663</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -7382,7 +7382,7 @@
         <v>1.592719558542871e-06</v>
       </c>
       <c r="H34" t="n">
-        <v>99.99996360706962</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>4</v>
@@ -7403,17 +7403,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.2031</t>
+          <t>1.2822</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.031</t>
+          <t>1.095</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.404</t>
+          <t>1.502</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -7423,7 +7423,7 @@
         <v>0.00158215660418437</v>
       </c>
       <c r="H35" t="n">
-        <v>99.99982965062681</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>4</v>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.2565</t>
+          <t>1.2647</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.631</t>
         </is>
       </c>
       <c r="F36" t="b">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>99.99998493565828</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>99.99801771045323</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>4</v>
@@ -7485,17 +7485,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.1224</t>
+          <t>1.1393</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.730</t>
+          <t>0.740</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1.754</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -7505,7 +7505,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>99.99881055196656</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>4</v>
@@ -7806,17 +7806,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.1539</t>
+          <t>1.1959</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.050</t>
+          <t>1.086</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.268</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -7826,7 +7826,7 @@
         <v>1.592719558542871e-06</v>
       </c>
       <c r="H46" t="n">
-        <v>38.52515852264099</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>4</v>
@@ -7888,24 +7888,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0.6589</t>
+          <t>0.6445</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>0.494</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.842</t>
         </is>
       </c>
       <c r="F48" t="b">
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>99.99998493565828</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0.002196355696408192</v>
@@ -8381,17 +8381,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.0102</t>
+          <t>3.1946</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.119</t>
+          <t>2.246</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.276</t>
+          <t>4.544</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -8401,7 +8401,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>99.99999803708718</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>22</v>
@@ -8463,17 +8463,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.0133</t>
+          <t>1.0288</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>0.379</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.751</t>
+          <t>2.794</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -8483,7 +8483,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>99.99372184353503</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -8825,27 +8825,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.0247</t>
+          <t>1.0552</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>0.909</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>1.225</t>
         </is>
       </c>
       <c r="F23" t="b">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>89.05825463352933</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>99.99999803708718</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>22</v>
@@ -8866,24 +8866,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.7682</t>
+          <t>0.7525</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.611</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.944</t>
+          <t>0.927</t>
         </is>
       </c>
       <c r="F24" t="b">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>99.97344800904655</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0.00288422364583929</v>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.2180</t>
+          <t>1.2225</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -8917,17 +8917,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.627</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="F25" t="b">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>99.96015548986463</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>99.99372184353503</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>22</v>
@@ -9269,17 +9269,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.1830</t>
+          <t>1.2554</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>1.084</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -9289,7 +9289,7 @@
         <v>62.15076815742187</v>
       </c>
       <c r="H35" t="n">
-        <v>99.99999803708718</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>22</v>
@@ -9310,24 +9310,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.1584</t>
+          <t>1.1309</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>0.904</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.444</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="F36" t="b">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>99.99503978336416</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0.00288422364583929</v>
@@ -9339,7 +9339,7 @@
         <v>22</v>
       </c>
       <c r="K36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -9351,17 +9351,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.6516</t>
+          <t>1.6744</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.098</t>
+          <t>1.112</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.484</t>
+          <t>2.522</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -9371,7 +9371,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>99.99372184353503</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>22</v>
@@ -9713,17 +9713,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.1545</t>
+          <t>1.1897</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.980</t>
+          <t>1.006</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.361</t>
+          <t>1.406</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -9733,7 +9733,7 @@
         <v>62.15076815742187</v>
       </c>
       <c r="H47" t="n">
-        <v>89.05825463352933</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>22</v>
@@ -9754,27 +9754,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.5080</t>
+          <t>1.5029</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.190</t>
+          <t>1.178</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.912</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="F48" t="b">
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>99.99503978336416</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>99.97344800904655</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>22</v>
@@ -9795,17 +9795,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.3560</t>
+          <t>1.3696</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>0.899</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2.064</t>
+          <t>2.087</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -9815,7 +9815,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>99.96015548986463</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>22</v>
@@ -10206,27 +10206,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.8123</t>
+          <t>0.7257</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>0.533</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>0.988</t>
         </is>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>99.99999999000001</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>99.99999971390291</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>22</v>
@@ -10247,17 +10247,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.3476</t>
+          <t>1.4276</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.945</t>
+          <t>0.999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.923</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -10267,7 +10267,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>99.99994153729666</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>22</v>
@@ -10288,17 +10288,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.8599</t>
+          <t>0.8876</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.425</t>
+          <t>0.438</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.741</t>
+          <t>1.799</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -10308,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>99.99999916573678</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -10650,27 +10650,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.9105</t>
+          <t>0.9543</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>0.866</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>1.051</t>
         </is>
       </c>
       <c r="F22" t="b">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>99.99999341688996</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>99.99999971390291</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>22</v>
@@ -10691,27 +10691,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.2654</t>
+          <t>1.2930</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.098</t>
+          <t>1.113</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="F23" t="b">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>99.996277246481</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>99.99994153729666</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>22</v>
@@ -10732,27 +10732,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.1252</t>
+          <t>1.1370</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>0.905</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="F24" t="b">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>99.99525725585139</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>99.99999916573678</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>22</v>
@@ -10773,24 +10773,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.5440</t>
+          <t>0.5389</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.394</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="F25" t="b">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>99.99923978474666</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0.0007096613591267564</v>
@@ -11094,27 +11094,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.9743</t>
+          <t>1.1041</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>1.010</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>1.206</t>
         </is>
       </c>
       <c r="F34" t="b">
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>19.81185314384397</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>99.99999971390291</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>22</v>
@@ -11135,27 +11135,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.3261</t>
+          <t>1.3606</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.143</t>
+          <t>1.164</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.539</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="F35" t="b">
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>99.98669975490962</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>99.99994153729666</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>22</v>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.6560</t>
+          <t>1.6672</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -11186,17 +11186,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2.088</t>
+          <t>2.116</t>
         </is>
       </c>
       <c r="F36" t="b">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>99.99979978102513</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>99.99999916573678</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>22</v>
@@ -11538,27 +11538,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.0700</t>
+          <t>1.1569</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.977</t>
+          <t>1.049</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.172</t>
+          <t>1.276</t>
         </is>
       </c>
       <c r="F46" t="b">
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>19.81185314384397</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>99.99999341688996</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>22</v>
@@ -11579,27 +11579,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.0480</t>
+          <t>1.0523</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>0.884</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.239</t>
+          <t>1.252</t>
         </is>
       </c>
       <c r="F47" t="b">
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>99.98669975490962</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>99.996277246481</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>22</v>
@@ -11620,27 +11620,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.4717</t>
+          <t>1.4663</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.135</t>
+          <t>1.124</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.913</t>
         </is>
       </c>
       <c r="F48" t="b">
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>99.99979978102513</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>99.99525725585139</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>22</v>
@@ -11661,17 +11661,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.5183</t>
+          <t>1.5326</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>1.015</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2.289</t>
+          <t>2.314</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -11681,7 +11681,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>99.99923978474666</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>22</v>
@@ -11982,17 +11982,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2.4413</t>
+          <t>2.8088</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2.019</t>
+          <t>2.316</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2.952</t>
+          <t>3.406</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -12002,7 +12002,7 @@
         <v>0.0004117208146238172</v>
       </c>
       <c r="H58" t="n">
-        <v>99.99999971390291</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>22</v>
@@ -12011,7 +12011,7 @@
         <v>22</v>
       </c>
       <c r="K58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -12023,27 +12023,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0.7422</t>
+          <t>0.7242</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>0.506</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.023</t>
+          <t>1.036</t>
         </is>
       </c>
       <c r="F59" t="b">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>99.99999999000001</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>99.99994153729666</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
         <v>22</v>
@@ -12064,17 +12064,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1.1505</t>
+          <t>1.1835</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>0.576</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2.361</t>
+          <t>2.431</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>99.99999916573678</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>22</v>
@@ -12426,17 +12426,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2.6812</t>
+          <t>2.9432</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2.208</t>
+          <t>2.417</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>3.256</t>
+          <t>3.585</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -12446,7 +12446,7 @@
         <v>0.0004117208146238172</v>
       </c>
       <c r="H70" t="n">
-        <v>99.99999341688996</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
         <v>22</v>
@@ -12467,27 +12467,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0.5866</t>
+          <t>0.5601</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>0.389</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>0.807</t>
         </is>
       </c>
       <c r="F71" t="b">
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>99.99999999000001</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>99.996277246481</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
         <v>22</v>
@@ -12508,17 +12508,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1.0225</t>
+          <t>1.0409</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>0.502</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2.119</t>
+          <t>2.159</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -12528,7 +12528,7 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>99.99525725585139</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
         <v>22</v>
@@ -12549,17 +12549,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>5.3330</t>
+          <t>5.3897</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1.946</t>
+          <t>1.965</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>14.616</t>
+          <t>14.781</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -12569,7 +12569,7 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>99.99923978474666</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -12870,17 +12870,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2.5057</t>
+          <t>2.5441</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2.066</t>
+          <t>2.097</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>3.039</t>
+          <t>3.087</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -12890,7 +12890,7 @@
         <v>0.0004117208146238172</v>
       </c>
       <c r="H82" t="n">
-        <v>19.81185314384397</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
         <v>22</v>
@@ -12911,27 +12911,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.5597</t>
+          <t>0.5323</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>0.770</t>
         </is>
       </c>
       <c r="F83" t="b">
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>99.99999999000001</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>99.98669975490962</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
         <v>22</v>
@@ -12952,17 +12952,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.6948</t>
+          <t>0.7099</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.444</t>
+          <t>1.477</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -12972,7 +12972,7 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>99.99979978102513</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
         <v>22</v>
@@ -13072,7 +13072,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DELTA_INAPPLICABLE</t>
+          <t>INSUFFICIENT_SIGNAL</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -13184,10 +13184,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -13238,10 +13238,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
@@ -13265,10 +13265,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
@@ -14927,38 +14927,36 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>99.99836701224508</v>
+        <v>99.89803107234498</v>
       </c>
       <c r="M20" t="n">
-        <v>99.99836701224508</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>99.99836701224508</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>99.99836701224508</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>1.857918797720702e-05</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0.2447791366789677</v>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>0.00163346758135682</v>
+        <v>0.001467078559092024</v>
       </c>
       <c r="S20" t="n">
-        <v>0.001114210250503705</v>
+        <v>0.0009750436212635123</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0001056016389969581</v>
+        <v>2.624452291287189e-05</v>
       </c>
       <c r="U20" t="n">
-        <v>0.001080148172350531</v>
+        <v>0.0009458711353828253</v>
       </c>
       <c r="V20" t="n">
         <v>45</v>
@@ -15009,11 +15007,11 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>99.98082748850817</v>
+        <v>0.0005314895659107588</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -15027,9 +15025,7 @@
       <c r="P21" t="n">
         <v>1.866051916918061e-05</v>
       </c>
-      <c r="Q21" t="n">
-        <v>13927914.16784326</v>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
         <v>0.001598895696833926</v>
       </c>
@@ -15091,38 +15087,36 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>67.15278858582882</v>
+        <v>99.99604338082898</v>
       </c>
       <c r="M22" t="n">
-        <v>67.15278858582882</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>67.15278858582882</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>67.15278858582882</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>2.670577428594451e-05</v>
       </c>
-      <c r="Q22" t="n">
-        <v>14766364.29839349</v>
-      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>0.001722193049745661</v>
+        <v>0.001591851093980468</v>
       </c>
       <c r="S22" t="n">
-        <v>0.001189969912825443</v>
+        <v>0.001076721425630619</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0002275462145916859</v>
+        <v>0.0001741717392829618</v>
       </c>
       <c r="U22" t="n">
-        <v>0.001149665262185615</v>
+        <v>0.001041921884216244</v>
       </c>
       <c r="V22" t="n">
         <v>45</v>
@@ -17451,38 +17445,36 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>20.17276949813065</v>
+        <v>0.002450913499673524</v>
       </c>
       <c r="M51" t="n">
-        <v>20.17276949813065</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>20.17276949813065</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>20.17276949813065</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
         <v>1.712831358017336e-05</v>
       </c>
-      <c r="Q51" t="n">
-        <v>8947471.209929135</v>
-      </c>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="n">
-        <v>0.001695889896326707</v>
+        <v>0.001653828431228948</v>
       </c>
       <c r="S51" t="n">
-        <v>0.001215350627910184</v>
+        <v>0.001180192856083302</v>
       </c>
       <c r="T51" t="n">
-        <v>6.822928405279572e-05</v>
+        <v>8.000746761023135e-05</v>
       </c>
       <c r="U51" t="n">
-        <v>0.001199116567817804</v>
+        <v>0.001164314193467678</v>
       </c>
       <c r="V51" t="n">
         <v>45</v>
@@ -17773,7 +17765,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -18335,38 +18327,36 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0.4381125719082086</v>
+        <v>1.278761050355924e-10</v>
       </c>
       <c r="M62" t="n">
-        <v>0.4381125719082086</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>0.4381125719082086</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>0.4381125719082086</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
         <v>0.006028409511812455</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0.190690661639951</v>
-      </c>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="n">
-        <v>0.7057971357643902</v>
+        <v>0.5872347740240069</v>
       </c>
       <c r="S62" t="n">
-        <v>0.4542934887457543</v>
+        <v>0.3670636316124459</v>
       </c>
       <c r="T62" t="n">
-        <v>0.02161838133580918</v>
+        <v>0.04441756303840405</v>
       </c>
       <c r="U62" t="n">
-        <v>0.4755439613080352</v>
+        <v>0.3836213737902346</v>
       </c>
       <c r="V62" t="n">
         <v>41</v>
@@ -18417,38 +18407,36 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.368184590370468</v>
+        <v>8.945047182007545e-15</v>
       </c>
       <c r="M63" t="n">
-        <v>0.368184590370468</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0.368184590370468</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>0.368184590370468</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
         <v>0.006041416232669848</v>
       </c>
-      <c r="Q63" t="n">
-        <v>1281490779.838289</v>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="n">
-        <v>0.5480529557596417</v>
+        <v>0.4830169501854772</v>
       </c>
       <c r="S63" t="n">
-        <v>0.3537164742715944</v>
+        <v>0.3035211287507119</v>
       </c>
       <c r="T63" t="n">
-        <v>0.05194639051618588</v>
+        <v>0.01522610864425911</v>
       </c>
       <c r="U63" t="n">
-        <v>0.3698125409926292</v>
+        <v>0.3176971655586485</v>
       </c>
       <c r="V63" t="n">
         <v>41</v>
@@ -19811,38 +19799,36 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>99.99999874596539</v>
+        <v>99.99315761885542</v>
       </c>
       <c r="M80" t="n">
-        <v>99.99999874596539</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>99.99999874596539</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>99.99999874596539</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
         <v>2.410448287007926e-05</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0.273595803050369</v>
-      </c>
+      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="n">
-        <v>0.001938011527537108</v>
+        <v>0.001716144095571411</v>
       </c>
       <c r="S80" t="n">
-        <v>0.00124428403281424</v>
+        <v>0.001075797348003461</v>
       </c>
       <c r="T80" t="n">
-        <v>8.490851128771211e-05</v>
+        <v>2.646742971968569e-05</v>
       </c>
       <c r="U80" t="n">
-        <v>0.00130236131674547</v>
+        <v>0.001126349212955512</v>
       </c>
       <c r="V80" t="n">
         <v>41</v>
@@ -19893,38 +19879,36 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.004735882525673585</v>
+        <v>99.9998928058157</v>
       </c>
       <c r="M81" t="n">
-        <v>0.004735882525673585</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>0.004735882525673585</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>0.004735882525673585</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
         <v>1.006199791036633e-05</v>
       </c>
-      <c r="Q81" t="n">
-        <v>1592103.743332472</v>
-      </c>
+      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="n">
-        <v>0.0007968359450181702</v>
+        <v>0.0007968338020428505</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0005261200987242614</v>
+        <v>0.0005261183540943751</v>
       </c>
       <c r="T81" t="n">
-        <v>9.882015128152496e-05</v>
+        <v>9.881858132556286e-05</v>
       </c>
       <c r="U81" t="n">
-        <v>0.0005491555906107161</v>
+        <v>0.0005491538105611956</v>
       </c>
       <c r="V81" t="n">
         <v>41</v>
@@ -20057,38 +20041,36 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>99.98397501305337</v>
+        <v>98.75610295753103</v>
       </c>
       <c r="M83" t="n">
-        <v>99.98397501305337</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>99.98397501305337</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>99.98397501305337</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
         <v>8.630764042192715e-06</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0.5416440336051862</v>
-      </c>
+      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="n">
-        <v>0.0007645859154417622</v>
+        <v>0.0007263137477559209</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0004942381645320634</v>
+        <v>0.0004649630714829625</v>
       </c>
       <c r="T83" t="n">
-        <v>4.430887812567272e-05</v>
+        <v>3.176907030865317e-05</v>
       </c>
       <c r="U83" t="n">
-        <v>0.0005172417758557939</v>
+        <v>0.0004866826278176599</v>
       </c>
       <c r="V83" t="n">
         <v>41</v>
@@ -20385,11 +20367,11 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>99.98869119254518</v>
+        <v>99.3020403130092</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -20403,9 +20385,7 @@
       <c r="P87" t="n">
         <v>6.485511828967794e-06</v>
       </c>
-      <c r="Q87" t="n">
-        <v>6255021.703480332</v>
-      </c>
+      <c r="Q87" t="inlineStr"/>
       <c r="R87" t="n">
         <v>0.0005515883915342586</v>
       </c>
@@ -20467,11 +20447,11 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>99.9989016016915</v>
+        <v>5.711663740193273e-05</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -20485,9 +20465,7 @@
       <c r="P88" t="n">
         <v>2.451821705490913e-05</v>
       </c>
-      <c r="Q88" t="n">
-        <v>19408134.82491929</v>
-      </c>
+      <c r="Q88" t="inlineStr"/>
       <c r="R88" t="n">
         <v>0.002237294645361168</v>
       </c>
@@ -20795,38 +20773,36 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.4537941446299353</v>
+        <v>3.23273682366202e-12</v>
       </c>
       <c r="M92" t="n">
-        <v>0.4537941446299353</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>0.4537941446299353</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>0.4537941446299353</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
         <v>0.006013021016645737</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0.2053037849078561</v>
-      </c>
+      <c r="Q92" t="inlineStr"/>
       <c r="R92" t="n">
-        <v>0.7840396962739421</v>
+        <v>0.6513349590144611</v>
       </c>
       <c r="S92" t="n">
-        <v>0.3810602543943351</v>
+        <v>0.3051981445436431</v>
       </c>
       <c r="T92" t="n">
-        <v>0.02318843586393549</v>
+        <v>0.04283588671188832</v>
       </c>
       <c r="U92" t="n">
-        <v>0.4761401898876165</v>
+        <v>0.3802972005941919</v>
       </c>
       <c r="V92" t="n">
         <v>35</v>
@@ -21369,38 +21345,36 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>5.144869335656168</v>
+        <v>7.100089660627878</v>
       </c>
       <c r="M99" t="n">
-        <v>5.144869335656168</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>5.144869335656168</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>5.144869335656168</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
         <v>0.001212733279543603</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0.2926929975019416</v>
-      </c>
+      <c r="Q99" t="inlineStr"/>
       <c r="R99" t="n">
-        <v>0.1078019264456274</v>
+        <v>0.08222782261162327</v>
       </c>
       <c r="S99" t="n">
-        <v>0.05457194168178857</v>
+        <v>0.03897772604259196</v>
       </c>
       <c r="T99" t="n">
-        <v>0.009002522277096664</v>
+        <v>0.001463525737282649</v>
       </c>
       <c r="U99" t="n">
-        <v>0.06804964171747295</v>
+        <v>0.04870882681814144</v>
       </c>
       <c r="V99" t="n">
         <v>35</v>
@@ -21615,38 +21589,36 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>12.94399970085989</v>
+        <v>3.876759057336397e-07</v>
       </c>
       <c r="M102" t="n">
-        <v>12.94399970085989</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>12.94399970085989</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>12.94399970085989</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
         <v>0.0004781921699441366</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0.276495883647545</v>
-      </c>
+      <c r="Q102" t="inlineStr"/>
       <c r="R102" t="n">
-        <v>0.04199901033481993</v>
+        <v>0.0321830166491119</v>
       </c>
       <c r="S102" t="n">
-        <v>0.02117740292989744</v>
+        <v>0.01522063651010338</v>
       </c>
       <c r="T102" t="n">
-        <v>0.002978172244975777</v>
+        <v>0.0007795757489196533</v>
       </c>
       <c r="U102" t="n">
-        <v>0.02641940342858014</v>
+        <v>0.01901992103434821</v>
       </c>
       <c r="V102" t="n">
         <v>35</v>
@@ -22271,20 +22243,20 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L110" t="n">
         <v>99.99832749090832</v>
       </c>
       <c r="M110" t="n">
-        <v>99.99832749090832</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>99.99832749090832</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>99.99832749090832</v>
+        <v>0</v>
       </c>
       <c r="P110" t="n">
         <v>2.483947791541276e-05</v>
@@ -22293,16 +22265,16 @@
         <v>0.234306827612376</v>
       </c>
       <c r="R110" t="n">
-        <v>0.002357012541565787</v>
+        <v>0.002070181323649837</v>
       </c>
       <c r="S110" t="n">
-        <v>0.001165694379217539</v>
+        <v>0.0009921092319155555</v>
       </c>
       <c r="T110" t="n">
-        <v>0.0001028130738700687</v>
+        <v>3.831768508750621e-05</v>
       </c>
       <c r="U110" t="n">
-        <v>0.001456206792707133</v>
+        <v>0.001239998601838677</v>
       </c>
       <c r="V110" t="n">
         <v>35</v>
@@ -22353,38 +22325,36 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>18.07141117982593</v>
+        <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>18.07141117982593</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>18.07141117982593</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>18.07141117982593</v>
+        <v>0</v>
       </c>
       <c r="P111" t="n">
         <v>1.133492938024884e-05</v>
       </c>
-      <c r="Q111" t="n">
-        <v>3664122.387808314</v>
-      </c>
+      <c r="Q111" t="inlineStr"/>
       <c r="R111" t="n">
-        <v>0.001255930794024005</v>
+        <v>0.001238663307138183</v>
       </c>
       <c r="S111" t="n">
-        <v>0.0006177383806401349</v>
+        <v>0.0006074867904251721</v>
       </c>
       <c r="T111" t="n">
-        <v>5.185802563996097e-05</v>
+        <v>5.573383524628498e-05</v>
       </c>
       <c r="U111" t="n">
-        <v>0.0007713032139580113</v>
+        <v>0.0007584375592510155</v>
       </c>
       <c r="V111" t="n">
         <v>35</v>
@@ -22517,38 +22487,36 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>99.99655614702037</v>
+        <v>99.3020403130092</v>
       </c>
       <c r="M113" t="n">
-        <v>99.99655614702037</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>99.99655614702037</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>99.99655614702037</v>
+        <v>0</v>
       </c>
       <c r="P113" t="n">
         <v>1.159122963878005e-05</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0.9187396558252575</v>
-      </c>
+      <c r="Q113" t="inlineStr"/>
       <c r="R113" t="n">
-        <v>0.0009943689457676606</v>
+        <v>0.0009380057570229976</v>
       </c>
       <c r="S113" t="n">
-        <v>0.0004907480820797233</v>
+        <v>0.0004567226564730005</v>
       </c>
       <c r="T113" t="n">
-        <v>3.074052882887063e-05</v>
+        <v>2.190425871369077e-05</v>
       </c>
       <c r="U113" t="n">
-        <v>0.0006132533836291775</v>
+        <v>0.0005707606261452159</v>
       </c>
       <c r="V113" t="n">
         <v>35</v>
@@ -22599,38 +22567,36 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>99.99883438093936</v>
+        <v>99.3020403130092</v>
       </c>
       <c r="M114" t="n">
-        <v>99.99883438093936</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>99.99883438093936</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>99.99883438093936</v>
+        <v>0</v>
       </c>
       <c r="P114" t="n">
         <v>5.189293034177101e-06</v>
       </c>
-      <c r="Q114" t="n">
-        <v>3586070.13751977</v>
-      </c>
+      <c r="Q114" t="inlineStr"/>
       <c r="R114" t="n">
-        <v>0.0005219254156982111</v>
+        <v>0.0005055773466846192</v>
       </c>
       <c r="S114" t="n">
-        <v>0.0002672525634914902</v>
+        <v>0.0002570638138923832</v>
       </c>
       <c r="T114" t="n">
-        <v>5.337654059309692e-05</v>
+        <v>4.892264629836939e-05</v>
       </c>
       <c r="U114" t="n">
-        <v>0.0003330304637794277</v>
+        <v>0.0003204102458501164</v>
       </c>
       <c r="V114" t="n">
         <v>35</v>
@@ -22681,38 +22647,36 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>73.33347320005834</v>
+        <v>99.3020403130092</v>
       </c>
       <c r="M115" t="n">
-        <v>73.33347320005834</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>73.33347320005834</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>73.33347320005834</v>
+        <v>0</v>
       </c>
       <c r="P115" t="n">
         <v>8.608843789610296e-06</v>
       </c>
-      <c r="Q115" t="n">
-        <v>3538910.768658287</v>
-      </c>
+      <c r="Q115" t="inlineStr"/>
       <c r="R115" t="n">
-        <v>0.0008725464356789725</v>
+        <v>0.0008393752056345484</v>
       </c>
       <c r="S115" t="n">
-        <v>0.0004463848235045245</v>
+        <v>0.0004256795584865307</v>
       </c>
       <c r="T115" t="n">
-        <v>6.49018135431961e-05</v>
+        <v>5.67753006828295e-05</v>
       </c>
       <c r="U115" t="n">
-        <v>0.0005569304906200015</v>
+        <v>0.000531279374617475</v>
       </c>
       <c r="V115" t="n">
         <v>35</v>
@@ -22763,38 +22727,36 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>99.88585064778931</v>
+        <v>57.24173631838615</v>
       </c>
       <c r="M116" t="n">
-        <v>99.88585064778931</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>99.88585064778931</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>99.88585064778931</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
         <v>4.326630580658509e-06</v>
       </c>
-      <c r="Q116" t="n">
-        <v>833048.4074225093</v>
-      </c>
+      <c r="Q116" t="inlineStr"/>
       <c r="R116" t="n">
-        <v>0.000439938919140674</v>
+        <v>0.0004284616947221984</v>
       </c>
       <c r="S116" t="n">
-        <v>0.0002148986013965135</v>
+        <v>0.0002080468403985156</v>
       </c>
       <c r="T116" t="n">
-        <v>9.665022184634727e-06</v>
+        <v>1.020079760668863e-05</v>
       </c>
       <c r="U116" t="n">
-        <v>0.0002685860833727325</v>
+        <v>0.000259999796873299</v>
       </c>
       <c r="V116" t="n">
         <v>35</v>
@@ -22927,7 +22889,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L118" t="n">
@@ -22945,9 +22907,7 @@
       <c r="P118" t="n">
         <v>2.82701175668801e-05</v>
       </c>
-      <c r="Q118" t="n">
-        <v>18994601.36082338</v>
-      </c>
+      <c r="Q118" t="inlineStr"/>
       <c r="R118" t="n">
         <v>0.0007914309582418585</v>
       </c>
@@ -23337,38 +23297,36 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0.4324265093155894</v>
+        <v>5.022565752920349e-11</v>
       </c>
       <c r="M123" t="n">
-        <v>0.4324265093155894</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>0.4324265093155894</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>0.4324265093155894</v>
+        <v>0</v>
       </c>
       <c r="P123" t="n">
         <v>0.005987173046325693</v>
       </c>
-      <c r="Q123" t="n">
-        <v>3208408205.468919</v>
-      </c>
+      <c r="Q123" t="inlineStr"/>
       <c r="R123" t="n">
-        <v>0.3741162574892581</v>
+        <v>0.3398878015445518</v>
       </c>
       <c r="S123" t="n">
-        <v>0.2082634105991247</v>
+        <v>0.1820590970145115</v>
       </c>
       <c r="T123" t="n">
-        <v>0.08975775768330374</v>
+        <v>0.05659927752523886</v>
       </c>
       <c r="U123" t="n">
-        <v>0.3245245259969843</v>
+        <v>0.2854377500649131</v>
       </c>
       <c r="V123" t="n">
         <v>34</v>
@@ -24649,38 +24607,36 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>27.49288398547458</v>
+        <v>8.531769115521261e-10</v>
       </c>
       <c r="M139" t="n">
-        <v>27.49288398547458</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>27.49288398547458</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>27.49288398547458</v>
+        <v>0</v>
       </c>
       <c r="P139" t="n">
         <v>0.0004185777354576049</v>
       </c>
-      <c r="Q139" t="n">
-        <v>70148887.23567463</v>
-      </c>
+      <c r="Q139" t="inlineStr"/>
       <c r="R139" t="n">
-        <v>0.02634880500122358</v>
+        <v>0.01878445972775438</v>
       </c>
       <c r="S139" t="n">
-        <v>0.01421937927335543</v>
+        <v>0.009126083727519309</v>
       </c>
       <c r="T139" t="n">
-        <v>0.003372141441029104</v>
+        <v>0.0008576958932341753</v>
       </c>
       <c r="U139" t="n">
-        <v>0.02235251881784544</v>
+        <v>0.01440497160124364</v>
       </c>
       <c r="V139" t="n">
         <v>34</v>
@@ -24895,38 +24851,36 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L142" t="n">
         <v>99.99996360706962</v>
       </c>
       <c r="M142" t="n">
-        <v>99.99996360706962</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>99.99996360706962</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>99.99996360706962</v>
+        <v>0</v>
       </c>
       <c r="P142" t="n">
         <v>7.848967307763466e-05</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0.2919452869008161</v>
-      </c>
+      <c r="Q142" t="inlineStr"/>
       <c r="R142" t="n">
-        <v>0.005071203133966255</v>
+        <v>0.00392007475394973</v>
       </c>
       <c r="S142" t="n">
-        <v>0.00277129275109098</v>
+        <v>0.001990112621872396</v>
       </c>
       <c r="T142" t="n">
-        <v>0.0004973419972213941</v>
+        <v>9.486809831860035e-05</v>
       </c>
       <c r="U142" t="n">
-        <v>0.00436593221284905</v>
+        <v>0.003143283040122563</v>
       </c>
       <c r="V142" t="n">
         <v>34</v>
@@ -24977,38 +24931,36 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>78.68485143096366</v>
+        <v>99.99999442246379</v>
       </c>
       <c r="M143" t="n">
-        <v>78.68485143096366</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>78.68485143096366</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>78.68485143096366</v>
+        <v>0</v>
       </c>
       <c r="P143" t="n">
         <v>0.0001635415500933215</v>
       </c>
-      <c r="Q143" t="n">
-        <v>58043967.00968617</v>
-      </c>
+      <c r="Q143" t="inlineStr"/>
       <c r="R143" t="n">
-        <v>0.0103122108976768</v>
+        <v>0.007143808121774246</v>
       </c>
       <c r="S143" t="n">
-        <v>0.005442930061592062</v>
+        <v>0.003408817500397292</v>
       </c>
       <c r="T143" t="n">
-        <v>0.0008552971663018383</v>
+        <v>0.0005485123809050255</v>
       </c>
       <c r="U143" t="n">
-        <v>0.008585204343096483</v>
+        <v>0.005368819913262519</v>
       </c>
       <c r="V143" t="n">
         <v>34</v>
@@ -25059,38 +25011,36 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>38.52515852264099</v>
+        <v>0.006166637070935121</v>
       </c>
       <c r="M144" t="n">
-        <v>38.52515852264099</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>38.52515852264099</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>38.52515852264099</v>
+        <v>0</v>
       </c>
       <c r="P144" t="n">
         <v>3.753280708013851e-05</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0.2432067289276859</v>
-      </c>
+      <c r="Q144" t="inlineStr"/>
       <c r="R144" t="n">
-        <v>0.002593839597142213</v>
+        <v>0.002442445064453101</v>
       </c>
       <c r="S144" t="n">
-        <v>0.001373217213489001</v>
+        <v>0.001270677376393683</v>
       </c>
       <c r="T144" t="n">
-        <v>0.0001008489705010066</v>
+        <v>2.562494254889063e-05</v>
       </c>
       <c r="U144" t="n">
-        <v>0.002168728924451103</v>
+        <v>0.002007540185029948</v>
       </c>
       <c r="V144" t="n">
         <v>34</v>
@@ -25223,38 +25173,36 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L146" t="n">
         <v>99.99982965062681</v>
       </c>
       <c r="M146" t="n">
-        <v>99.99982965062681</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>99.99982965062681</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>99.99982965062681</v>
+        <v>0</v>
       </c>
       <c r="P146" t="n">
         <v>2.921257405690759e-05</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0.4838199195311653</v>
-      </c>
+      <c r="Q146" t="inlineStr"/>
       <c r="R146" t="n">
-        <v>0.001790366265953686</v>
+        <v>0.001614439763129629</v>
       </c>
       <c r="S146" t="n">
-        <v>0.0009460837864889542</v>
+        <v>0.0008273740537738369</v>
       </c>
       <c r="T146" t="n">
-        <v>9.260140100443397e-05</v>
+        <v>3.721015607047206e-05</v>
       </c>
       <c r="U146" t="n">
-        <v>0.001493613371025049</v>
+        <v>0.001307121018856324</v>
       </c>
       <c r="V146" t="n">
         <v>34</v>
@@ -25305,11 +25253,11 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>10.34958550447434</v>
+        <v>99.99999836563993</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -25323,9 +25271,7 @@
       <c r="P147" t="n">
         <v>3.938264210926682e-05</v>
       </c>
-      <c r="Q147" t="n">
-        <v>26269725.67056961</v>
-      </c>
+      <c r="Q147" t="inlineStr"/>
       <c r="R147" t="n">
         <v>0.002480124375580798</v>
       </c>
@@ -25551,38 +25497,36 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L150" t="n">
         <v>99.99801771045323</v>
       </c>
       <c r="M150" t="n">
-        <v>99.99801771045323</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>99.99801771045323</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>99.99801771045323</v>
+        <v>0</v>
       </c>
       <c r="P150" t="n">
         <v>1.420209271449045e-05</v>
       </c>
-      <c r="Q150" t="n">
-        <v>2469908.851115822</v>
-      </c>
+      <c r="Q150" t="inlineStr"/>
       <c r="R150" t="n">
-        <v>0.0008215888854591221</v>
+        <v>0.0007817314769607411</v>
       </c>
       <c r="S150" t="n">
-        <v>0.0004307418741004909</v>
+        <v>0.0004042827286834804</v>
       </c>
       <c r="T150" t="n">
-        <v>1.887292306433218e-05</v>
+        <v>1.887391897343444e-05</v>
       </c>
       <c r="U150" t="n">
-        <v>0.0006804619292039376</v>
+        <v>0.0006386167770636597</v>
       </c>
       <c r="V150" t="n">
         <v>34</v>
@@ -25791,38 +25735,36 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>99.99998493565828</v>
+        <v>0.0005116473984365655</v>
       </c>
       <c r="M153" t="n">
-        <v>99.99998493565828</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>99.99998493565828</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>99.99998493565828</v>
+        <v>0</v>
       </c>
       <c r="P153" t="n">
         <v>8.522180912716315e-06</v>
       </c>
-      <c r="Q153" t="n">
-        <v>4636390.631610394</v>
-      </c>
+      <c r="Q153" t="inlineStr"/>
       <c r="R153" t="n">
-        <v>0.0006500283924117827</v>
+        <v>0.0006246077017249942</v>
       </c>
       <c r="S153" t="n">
-        <v>0.0003443135722146441</v>
+        <v>0.000327816174634259</v>
       </c>
       <c r="T153" t="n">
-        <v>2.964000591648263e-05</v>
+        <v>3.783749483542175e-05</v>
       </c>
       <c r="U153" t="n">
-        <v>0.0005434317804474914</v>
+        <v>0.0005171450567757086</v>
       </c>
       <c r="V153" t="n">
         <v>34</v>
@@ -25873,38 +25815,36 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>99.99881055196656</v>
+        <v>99.23871421384499</v>
       </c>
       <c r="M154" t="n">
-        <v>99.99881055196656</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>99.99881055196656</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>99.99881055196656</v>
+        <v>0</v>
       </c>
       <c r="P154" t="n">
         <v>6.335042100090133e-06</v>
       </c>
-      <c r="Q154" t="n">
-        <v>3297662.181032485</v>
-      </c>
+      <c r="Q154" t="inlineStr"/>
       <c r="R154" t="n">
-        <v>0.0003846742011087939</v>
+        <v>0.0003757243948449169</v>
       </c>
       <c r="S154" t="n">
-        <v>0.0001953733419747284</v>
+        <v>0.0001896080617882982</v>
       </c>
       <c r="T154" t="n">
-        <v>1.244555220564182e-05</v>
+        <v>1.496445151053687e-05</v>
       </c>
       <c r="U154" t="n">
-        <v>0.0003085090956977543</v>
+        <v>0.0002993324262055668</v>
       </c>
       <c r="V154" t="n">
         <v>34</v>
@@ -25955,7 +25895,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L155" t="n">
@@ -25973,9 +25913,7 @@
       <c r="P155" t="n">
         <v>1.199127754394794e-05</v>
       </c>
-      <c r="Q155" t="n">
-        <v>11371255.20877764</v>
-      </c>
+      <c r="Q155" t="inlineStr"/>
       <c r="R155" t="n">
         <v>0.0003105253301246925</v>
       </c>
@@ -28497,38 +28435,36 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L186" t="n">
         <v>99.99999803708718</v>
       </c>
       <c r="M186" t="n">
-        <v>99.99999803708718</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>99.99999803708718</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
-        <v>99.99999803708718</v>
+        <v>0</v>
       </c>
       <c r="P186" t="n">
         <v>2.938959455028546e-05</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0.5091039728521236</v>
-      </c>
+      <c r="Q186" t="inlineStr"/>
       <c r="R186" t="n">
-        <v>0.001431397843017007</v>
+        <v>0.001320882144526264</v>
       </c>
       <c r="S186" t="n">
-        <v>0.0006671273655428144</v>
+        <v>0.0005956160331779327</v>
       </c>
       <c r="T186" t="n">
-        <v>6.558899011532143e-05</v>
+        <v>3.559526430164787e-05</v>
       </c>
       <c r="U186" t="n">
-        <v>0.001454792892308142</v>
+        <v>0.001299922129655748</v>
       </c>
       <c r="V186" t="n">
         <v>30</v>
@@ -28661,38 +28597,36 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L188" t="n">
-        <v>89.05825463352933</v>
+        <v>99.98618857108376</v>
       </c>
       <c r="M188" t="n">
-        <v>89.05825463352933</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>89.05825463352933</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
-        <v>89.05825463352933</v>
+        <v>0</v>
       </c>
       <c r="P188" t="n">
         <v>1.580741089325414e-05</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0.3590073916814031</v>
-      </c>
+      <c r="Q188" t="inlineStr"/>
       <c r="R188" t="n">
-        <v>0.0007914125089065911</v>
+        <v>0.0007593707413815071</v>
       </c>
       <c r="S188" t="n">
-        <v>0.0003769548897103433</v>
+        <v>0.0003551004861180686</v>
       </c>
       <c r="T188" t="n">
-        <v>4.648425192695484e-05</v>
+        <v>2.708959165528889e-05</v>
       </c>
       <c r="U188" t="n">
-        <v>0.0008211834407751577</v>
+        <v>0.0007744433956394527</v>
       </c>
       <c r="V188" t="n">
         <v>30</v>
@@ -28907,7 +28841,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L191" t="n">
@@ -28925,9 +28859,7 @@
       <c r="P191" t="n">
         <v>3.469442318178457e-05</v>
       </c>
-      <c r="Q191" t="n">
-        <v>29071139.37547025</v>
-      </c>
+      <c r="Q191" t="inlineStr"/>
       <c r="R191" t="n">
         <v>0.0007949568205817212</v>
       </c>
@@ -28989,38 +28921,36 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L192" t="n">
         <v>99.97344800904655</v>
       </c>
       <c r="M192" t="n">
-        <v>99.97344800904655</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>99.97344800904655</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
-        <v>99.97344800904655</v>
+        <v>0</v>
       </c>
       <c r="P192" t="n">
         <v>8.817038345936803e-06</v>
       </c>
-      <c r="Q192" t="n">
-        <v>1.425028811651335</v>
-      </c>
+      <c r="Q192" t="inlineStr"/>
       <c r="R192" t="n">
-        <v>0.0004528462042830653</v>
+        <v>0.0004411151320676545</v>
       </c>
       <c r="S192" t="n">
-        <v>0.0001993373511043683</v>
+        <v>0.000192518908537091</v>
       </c>
       <c r="T192" t="n">
-        <v>2.468565308148623e-05</v>
+        <v>2.855324086729275e-05</v>
       </c>
       <c r="U192" t="n">
-        <v>0.0004343090977486118</v>
+        <v>0.0004191199943399665</v>
       </c>
       <c r="V192" t="n">
         <v>30</v>
@@ -29071,20 +29001,20 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L193" t="n">
         <v>99.99503978336416</v>
       </c>
       <c r="M193" t="n">
-        <v>99.99503978336416</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>99.99503978336416</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
-        <v>99.99503978336416</v>
+        <v>0</v>
       </c>
       <c r="P193" t="n">
         <v>6.633179880177407e-06</v>
@@ -29093,16 +29023,16 @@
         <v>2864696.635007625</v>
       </c>
       <c r="R193" t="n">
-        <v>0.0005132602183423087</v>
+        <v>0.0004981803842975393</v>
       </c>
       <c r="S193" t="n">
-        <v>0.0002297082577631935</v>
+        <v>0.0002210129608862976</v>
       </c>
       <c r="T193" t="n">
-        <v>3.233102494539539e-05</v>
+        <v>3.686210989349765e-05</v>
       </c>
       <c r="U193" t="n">
-        <v>0.0004999671133173038</v>
+        <v>0.0004805218915453714</v>
       </c>
       <c r="V193" t="n">
         <v>30</v>
@@ -29153,38 +29083,36 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L194" t="n">
         <v>99.99372184353503</v>
       </c>
       <c r="M194" t="n">
-        <v>99.99372184353503</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>99.99372184353503</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
-        <v>99.99372184353503</v>
+        <v>0</v>
       </c>
       <c r="P194" t="n">
         <v>6.999245188682134e-06</v>
       </c>
-      <c r="Q194" t="n">
-        <v>3570851.499325457</v>
-      </c>
+      <c r="Q194" t="inlineStr"/>
       <c r="R194" t="n">
-        <v>0.0003060142813247015</v>
+        <v>0.0003005821327928658</v>
       </c>
       <c r="S194" t="n">
-        <v>0.0001356547567954825</v>
+        <v>0.0001323624927501625</v>
       </c>
       <c r="T194" t="n">
-        <v>1.122076225070992e-05</v>
+        <v>1.17334467738004e-05</v>
       </c>
       <c r="U194" t="n">
-        <v>0.0002958636339762149</v>
+        <v>0.0002886097740778493</v>
       </c>
       <c r="V194" t="n">
         <v>30</v>
@@ -29311,20 +29239,20 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L196" t="n">
         <v>99.96015548986463</v>
       </c>
       <c r="M196" t="n">
-        <v>99.96015548986463</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>99.96015548986463</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
-        <v>99.96015548986463</v>
+        <v>0</v>
       </c>
       <c r="P196" t="n">
         <v>4.079953198282405e-06</v>
@@ -29333,16 +29261,16 @@
         <v>2114622.310700125</v>
       </c>
       <c r="R196" t="n">
-        <v>0.0002264759587083437</v>
+        <v>0.0002234323104801488</v>
       </c>
       <c r="S196" t="n">
-        <v>0.0001056422134585498</v>
+        <v>0.0001036889507377813</v>
       </c>
       <c r="T196" t="n">
-        <v>7.284155627157517e-06</v>
+        <v>7.601530683317884e-06</v>
       </c>
       <c r="U196" t="n">
-        <v>0.0002304746802467088</v>
+        <v>0.0002262147439890981</v>
       </c>
       <c r="V196" t="n">
         <v>30</v>
@@ -31853,20 +31781,20 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L227" t="n">
         <v>99.99999971390291</v>
       </c>
       <c r="M227" t="n">
-        <v>99.99999971390291</v>
+        <v>0</v>
       </c>
       <c r="N227" t="n">
-        <v>99.99999971390291</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
-        <v>99.99999971390291</v>
+        <v>0</v>
       </c>
       <c r="P227" t="n">
         <v>6.772917316486888e-05</v>
@@ -31875,16 +31803,16 @@
         <v>0.2206651855977209</v>
       </c>
       <c r="R227" t="n">
-        <v>0.002327046401312462</v>
+        <v>0.002037488448961765</v>
       </c>
       <c r="S227" t="n">
-        <v>0.001320674793648838</v>
+        <v>0.001060488932150703</v>
       </c>
       <c r="T227" t="n">
-        <v>0.0001472408954395488</v>
+        <v>7.487557460020175e-05</v>
       </c>
       <c r="U227" t="n">
-        <v>0.003760740443133564</v>
+        <v>0.003024498178451425</v>
       </c>
       <c r="V227" t="n">
         <v>30</v>
@@ -31935,38 +31863,36 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L228" t="n">
-        <v>99.99999999000001</v>
+        <v>99.99999999992984</v>
       </c>
       <c r="M228" t="n">
-        <v>99.99999999000001</v>
+        <v>0</v>
       </c>
       <c r="N228" t="n">
-        <v>99.99999999000001</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
-        <v>99.99999999000001</v>
+        <v>0</v>
       </c>
       <c r="P228" t="n">
         <v>0.000170992578460419</v>
       </c>
-      <c r="Q228" t="n">
-        <v>70390850.09955239</v>
-      </c>
+      <c r="Q228" t="inlineStr"/>
       <c r="R228" t="n">
-        <v>0.004997297509286166</v>
+        <v>0.003908974465295457</v>
       </c>
       <c r="S228" t="n">
-        <v>0.002548711816751884</v>
+        <v>0.001746186479157552</v>
       </c>
       <c r="T228" t="n">
-        <v>0.0005411242033192985</v>
+        <v>0.0006925524551776896</v>
       </c>
       <c r="U228" t="n">
-        <v>0.007240936048058419</v>
+        <v>0.00490906086153269</v>
       </c>
       <c r="V228" t="n">
         <v>30</v>
@@ -32017,38 +31943,36 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L229" t="n">
         <v>99.99999341688996</v>
       </c>
       <c r="M229" t="n">
-        <v>99.99999341688996</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>99.99999341688996</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
-        <v>99.99999341688996</v>
+        <v>0</v>
       </c>
       <c r="P229" t="n">
         <v>4.783315080175279e-05</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0.3504693534553042</v>
-      </c>
+      <c r="Q229" t="inlineStr"/>
       <c r="R229" t="n">
-        <v>0.001519522650235268</v>
+        <v>0.00138819057162991</v>
       </c>
       <c r="S229" t="n">
-        <v>0.000857356434479111</v>
+        <v>0.0007367977815809061</v>
       </c>
       <c r="T229" t="n">
-        <v>9.982308602006669e-05</v>
+        <v>3.213355731554804e-05</v>
       </c>
       <c r="U229" t="n">
-        <v>0.002441836229918237</v>
+        <v>0.002101987964528366</v>
       </c>
       <c r="V229" t="n">
         <v>30</v>
@@ -32099,38 +32023,36 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L230" t="n">
-        <v>19.81185314384397</v>
+        <v>25.38225861862774</v>
       </c>
       <c r="M230" t="n">
-        <v>19.81185314384397</v>
+        <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>19.81185314384397</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
-        <v>19.81185314384397</v>
+        <v>0</v>
       </c>
       <c r="P230" t="n">
         <v>3.406160417725151e-05</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0.2340683620106587</v>
-      </c>
+      <c r="Q230" t="inlineStr"/>
       <c r="R230" t="n">
-        <v>0.00111307356336778</v>
+        <v>0.001097408926170615</v>
       </c>
       <c r="S230" t="n">
-        <v>0.0006248951510910768</v>
+        <v>0.0006101041734515625</v>
       </c>
       <c r="T230" t="n">
-        <v>5.324924377530638e-05</v>
+        <v>4.396469172088592e-05</v>
       </c>
       <c r="U230" t="n">
-        <v>0.001781255979998825</v>
+        <v>0.001739627484950403</v>
       </c>
       <c r="V230" t="n">
         <v>30</v>
@@ -32263,38 +32185,36 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L232" t="n">
         <v>99.99994153729666</v>
       </c>
       <c r="M232" t="n">
-        <v>99.99994153729666</v>
+        <v>0</v>
       </c>
       <c r="N232" t="n">
-        <v>99.99994153729666</v>
+        <v>0</v>
       </c>
       <c r="O232" t="n">
-        <v>99.99994153729666</v>
+        <v>0</v>
       </c>
       <c r="P232" t="n">
         <v>3.602800973964414e-05</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0.7614451852772578</v>
-      </c>
+      <c r="Q232" t="inlineStr"/>
       <c r="R232" t="n">
-        <v>0.0008932060210565528</v>
+        <v>0.0008457799193493762</v>
       </c>
       <c r="S232" t="n">
-        <v>0.0004917530180698051</v>
+        <v>0.0004485286151283934</v>
       </c>
       <c r="T232" t="n">
-        <v>6.174881707856969e-05</v>
+        <v>3.76430938859606e-05</v>
       </c>
       <c r="U232" t="n">
-        <v>0.001401328722750151</v>
+        <v>0.001279295396406319</v>
       </c>
       <c r="V232" t="n">
         <v>30</v>
@@ -32345,11 +32265,11 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L233" t="n">
-        <v>52.07399938339263</v>
+        <v>73.26228302528797</v>
       </c>
       <c r="M233" t="n">
         <v>0</v>
@@ -32363,9 +32283,7 @@
       <c r="P233" t="n">
         <v>5.345341205086612e-05</v>
       </c>
-      <c r="Q233" t="n">
-        <v>32735972.06057775</v>
-      </c>
+      <c r="Q233" t="inlineStr"/>
       <c r="R233" t="n">
         <v>0.001833380486925216</v>
       </c>
@@ -32427,38 +32345,36 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L234" t="n">
         <v>99.996277246481</v>
       </c>
       <c r="M234" t="n">
-        <v>99.996277246481</v>
+        <v>0</v>
       </c>
       <c r="N234" t="n">
-        <v>99.996277246481</v>
+        <v>0</v>
       </c>
       <c r="O234" t="n">
-        <v>99.996277246481</v>
+        <v>0</v>
       </c>
       <c r="P234" t="n">
         <v>1.704503059737354e-05</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0.4759636511517844</v>
-      </c>
+      <c r="Q234" t="inlineStr"/>
       <c r="R234" t="n">
-        <v>0.0005294230423122233</v>
+        <v>0.0005120772961609127</v>
       </c>
       <c r="S234" t="n">
-        <v>0.0002965110092956001</v>
+        <v>0.0002802444165488555</v>
       </c>
       <c r="T234" t="n">
-        <v>3.145345981249859e-05</v>
+        <v>2.132992279347656e-05</v>
       </c>
       <c r="U234" t="n">
-        <v>0.0008447921562627742</v>
+        <v>0.0007990325478955438</v>
       </c>
       <c r="V234" t="n">
         <v>30</v>
@@ -32509,38 +32425,36 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L235" t="n">
         <v>99.98669975490962</v>
       </c>
       <c r="M235" t="n">
-        <v>99.98669975490962</v>
+        <v>0</v>
       </c>
       <c r="N235" t="n">
-        <v>99.98669975490962</v>
+        <v>0</v>
       </c>
       <c r="O235" t="n">
-        <v>99.98669975490962</v>
+        <v>0</v>
       </c>
       <c r="P235" t="n">
         <v>1.431342172750345e-05</v>
       </c>
-      <c r="Q235" t="n">
-        <v>2626426.816829497</v>
-      </c>
+      <c r="Q235" t="inlineStr"/>
       <c r="R235" t="n">
-        <v>0.000469977757212239</v>
+        <v>0.0004562358103491702</v>
       </c>
       <c r="S235" t="n">
-        <v>0.0002632117076737572</v>
+        <v>0.0002501407978425201</v>
       </c>
       <c r="T235" t="n">
-        <v>2.762447331015348e-05</v>
+        <v>1.973946493678862e-05</v>
       </c>
       <c r="U235" t="n">
-        <v>0.0007494113835341903</v>
+        <v>0.0007128262705269853</v>
       </c>
       <c r="V235" t="n">
         <v>30</v>
@@ -32591,38 +32505,36 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L236" t="n">
-        <v>99.99999999000001</v>
+        <v>99.99999999483958</v>
       </c>
       <c r="M236" t="n">
-        <v>99.99999999000001</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>99.99999999000001</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
-        <v>99.99999999000001</v>
+        <v>0</v>
       </c>
       <c r="P236" t="n">
         <v>7.414931569872714e-05</v>
       </c>
-      <c r="Q236" t="n">
-        <v>38198811.96757618</v>
-      </c>
+      <c r="Q236" t="inlineStr"/>
       <c r="R236" t="n">
-        <v>0.00155645156276854</v>
+        <v>0.001424851037876168</v>
       </c>
       <c r="S236" t="n">
-        <v>0.000772656986167189</v>
+        <v>0.0006719607183687834</v>
       </c>
       <c r="T236" t="n">
-        <v>0.0002008288639484539</v>
+        <v>0.0001759775948256653</v>
       </c>
       <c r="U236" t="n">
-        <v>0.002190780829347365</v>
+        <v>0.001899105134438318</v>
       </c>
       <c r="V236" t="n">
         <v>30</v>
@@ -32673,38 +32585,36 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L237" t="n">
         <v>99.99999916573678</v>
       </c>
       <c r="M237" t="n">
-        <v>99.99999916573678</v>
+        <v>0</v>
       </c>
       <c r="N237" t="n">
-        <v>99.99999916573678</v>
+        <v>0</v>
       </c>
       <c r="O237" t="n">
-        <v>99.99999916573678</v>
+        <v>0</v>
       </c>
       <c r="P237" t="n">
         <v>1.687295514046056e-05</v>
       </c>
-      <c r="Q237" t="n">
-        <v>3076397.474506717</v>
-      </c>
+      <c r="Q237" t="inlineStr"/>
       <c r="R237" t="n">
-        <v>0.0004454153653581254</v>
+        <v>0.000433364620988219</v>
       </c>
       <c r="S237" t="n">
-        <v>0.0002337445164542082</v>
+        <v>0.0002234939958973909</v>
       </c>
       <c r="T237" t="n">
-        <v>1.66644782261631e-05</v>
+        <v>1.835722626385421e-05</v>
       </c>
       <c r="U237" t="n">
-        <v>0.000666705311783686</v>
+        <v>0.0006372878074706399</v>
       </c>
       <c r="V237" t="n">
         <v>30</v>
@@ -32831,38 +32741,36 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L239" t="n">
         <v>99.99525725585139</v>
       </c>
       <c r="M239" t="n">
-        <v>99.99525725585139</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>99.99525725585139</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
-        <v>99.99525725585139</v>
+        <v>0</v>
       </c>
       <c r="P239" t="n">
         <v>9.229630940260271e-06</v>
       </c>
-      <c r="Q239" t="n">
-        <v>1688692.847637749</v>
-      </c>
+      <c r="Q239" t="inlineStr"/>
       <c r="R239" t="n">
-        <v>0.0002753673085496699</v>
+        <v>0.0002707718845250956</v>
       </c>
       <c r="S239" t="n">
-        <v>0.0001380828465564839</v>
+        <v>0.0001343441064065541</v>
       </c>
       <c r="T239" t="n">
-        <v>1.537318350576018e-05</v>
+        <v>1.57995486963074e-05</v>
       </c>
       <c r="U239" t="n">
-        <v>0.0003935623537089095</v>
+        <v>0.0003827735474522296</v>
       </c>
       <c r="V239" t="n">
         <v>30</v>
@@ -32913,20 +32821,20 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L240" t="n">
         <v>99.99979978102513</v>
       </c>
       <c r="M240" t="n">
-        <v>99.99979978102513</v>
+        <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>99.99979978102513</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
-        <v>99.99979978102513</v>
+        <v>0</v>
       </c>
       <c r="P240" t="n">
         <v>7.360196266000505e-06</v>
@@ -32935,16 +32843,16 @@
         <v>2770403.084891323</v>
       </c>
       <c r="R240" t="n">
-        <v>0.000318983591557863</v>
+        <v>0.0003128303553876498</v>
       </c>
       <c r="S240" t="n">
-        <v>0.000160514255764453</v>
+        <v>0.0001557457448983109</v>
       </c>
       <c r="T240" t="n">
-        <v>2.913910356226763e-05</v>
+        <v>3.185940818841628e-05</v>
       </c>
       <c r="U240" t="n">
-        <v>0.0004562637752503819</v>
+        <v>0.0004422953356516692</v>
       </c>
       <c r="V240" t="n">
         <v>30</v>
@@ -32995,7 +32903,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L241" t="n">
@@ -33013,9 +32921,7 @@
       <c r="P241" t="n">
         <v>2.395439085816805e-05</v>
       </c>
-      <c r="Q241" t="n">
-        <v>21751739.7452101</v>
-      </c>
+      <c r="Q241" t="inlineStr"/>
       <c r="R241" t="n">
         <v>0.0006869516033407636</v>
       </c>
@@ -33235,38 +33141,36 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>delta_inapplicable</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L244" t="n">
         <v>99.99923978474666</v>
       </c>
       <c r="M244" t="n">
-        <v>99.99923978474666</v>
+        <v>0</v>
       </c>
       <c r="N244" t="n">
-        <v>99.99923978474666</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
-        <v>99.99923978474666</v>
+        <v>0</v>
       </c>
       <c r="P244" t="n">
         <v>6.036354065552406e-06</v>
       </c>
-      <c r="Q244" t="n">
-        <v>3431271.645127978</v>
-      </c>
+      <c r="Q244" t="inlineStr"/>
       <c r="R244" t="n">
-        <v>0.0001415070945738624</v>
+        <v>0.0001402356264045068</v>
       </c>
       <c r="S244" t="n">
-        <v>7.718264970584943e-05</v>
+        <v>7.603702586640407e-05</v>
       </c>
       <c r="T244" t="n">
-        <v>9.776568936260753e-06</v>
+        <v>9.137998758798719e-06</v>
       </c>
       <c r="U244" t="n">
-        <v>0.0002199269314165493</v>
+        <v>0.0002166707483838106</v>
       </c>
       <c r="V244" t="n">
         <v>30</v>

--- a/data/Czech/KCOR_summary.xlsx
+++ b/data/Czech/KCOR_summary.xlsx
@@ -540,17 +540,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.1935</t>
+          <t>1.2066</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.168</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.220</t>
+          <t>1.233</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -581,17 +581,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.9986</t>
+          <t>1.0161</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.918</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.086</t>
+          <t>1.105</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -622,17 +622,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.9987</t>
+          <t>1.0134</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.959</t>
+          <t>0.973</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.040</t>
+          <t>1.056</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -663,17 +663,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.4144</t>
+          <t>1.4317</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.372</t>
+          <t>1.388</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1.477</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -704,17 +704,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.4789</t>
+          <t>1.4896</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.377</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.600</t>
+          <t>1.612</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -745,24 +745,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.3978</t>
+          <t>1.3231</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1.142</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1.532</t>
         </is>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>32.43851239051246</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>31.82685917649427</v>
@@ -774,7 +774,7 @@
         <v>11</v>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -786,24 +786,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.9339</t>
+          <t>2.9678</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.303</t>
+          <t>2.330</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.737</t>
+          <t>3.780</t>
         </is>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>7.452380656070012e-05</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>48.31949007494163</v>
@@ -815,7 +815,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -827,17 +827,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.0730</t>
+          <t>1.0879</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.703</t>
+          <t>0.713</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.660</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -850,7 +850,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>11</v>
@@ -868,17 +868,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.3234</t>
+          <t>2.3549</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.384</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.900</t>
+          <t>3.954</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -909,17 +909,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12.6258</t>
+          <t>12.6752</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5.940</t>
+          <t>5.962</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26.839</t>
+          <t>26.946</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -984,17 +984,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.4264</t>
+          <t>1.4421</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.403</t>
+          <t>1.419</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.450</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.3338</t>
+          <t>1.3571</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.276</t>
+          <t>1.297</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.420</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.4474</t>
+          <t>1.4686</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.432</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.484</t>
+          <t>1.506</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.4748</t>
+          <t>1.4929</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.419</t>
+          <t>1.437</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.532</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.2250</t>
+          <t>1.2339</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.143</t>
+          <t>1.151</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.313</t>
+          <t>1.323</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.1889</t>
+          <t>1.2004</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.028</t>
+          <t>1.038</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.388</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1230,24 +1230,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.0850</t>
+          <t>1.0975</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.854</t>
+          <t>0.864</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.379</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F22" t="b">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0004379764066248792</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>48.31949007494163</v>
@@ -1259,7 +1259,7 @@
         <v>11</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.6223</t>
+          <t>0.6309</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>0.409</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.961</t>
+          <t>0.974</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.2343</t>
+          <t>1.2510</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>0.746</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.099</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1335,7 +1335,7 @@
         <v>0.06786025172366361</v>
       </c>
       <c r="I24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>11</v>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2.2733</t>
+          <t>2.2822</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.320</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16.215</t>
+          <t>16.279</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1633,17 +1633,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.8506</t>
+          <t>0.9072</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.699</t>
+          <t>0.740</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.035</t>
+          <t>1.112</t>
         </is>
       </c>
       <c r="F33" t="b">
@@ -1653,7 +1653,7 @@
         <v>2.237590263834829</v>
       </c>
       <c r="H33" t="n">
-        <v>32.43851239051246</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>11</v>
@@ -1662,7 +1662,7 @@
         <v>11</v>
       </c>
       <c r="K33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1691,10 +1691,10 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0004379764066248792</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>7.452380656070012e-05</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>11</v>
@@ -1703,7 +1703,7 @@
         <v>11</v>
       </c>
       <c r="K34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1741,7 +1741,7 @@
         <v>11</v>
       </c>
       <c r="J35" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1962,17 +1962,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.1706</t>
+          <t>1.1850</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>1.162</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1.208</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7844</t>
+          <t>0.7970</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.725</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.862</t>
+          <t>0.876</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -2044,17 +2044,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.0197</t>
+          <t>1.0364</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>0.985</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>1.090</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -2085,17 +2085,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.0808</t>
+          <t>1.0937</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>1.057</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>1.131</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.4705</t>
+          <t>1.4863</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.437</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.521</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -2167,17 +2167,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.4107</t>
+          <t>1.4266</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.342</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.499</t>
+          <t>1.516</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -2208,17 +2208,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.2429</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.095</t>
+          <t>1.105</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1.398</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -2249,17 +2249,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.1890</t>
+          <t>1.2066</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>0.948</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.513</t>
+          <t>1.536</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.0726</t>
+          <t>1.0902</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.650</t>
+          <t>0.660</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.771</t>
+          <t>1.801</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -2331,17 +2331,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7.3257</t>
+          <t>7.3475</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.001</t>
+          <t>4.013</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13.412</t>
+          <t>13.454</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -2406,17 +2406,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.1126</t>
+          <t>1.1262</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.097</t>
+          <t>1.110</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.128</t>
+          <t>1.142</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -2447,17 +2447,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.0074</t>
+          <t>1.0236</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.964</t>
+          <t>0.979</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.053</t>
+          <t>1.070</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -2488,17 +2488,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.0519</t>
+          <t>1.0691</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.026</t>
+          <t>1.042</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>1.097</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -2529,17 +2529,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.2643</t>
+          <t>1.2794</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.232</t>
+          <t>1.247</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.297</t>
+          <t>1.313</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -2570,17 +2570,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.0782</t>
+          <t>1.0898</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>1.038</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.132</t>
+          <t>1.144</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.2230</t>
+          <t>1.2368</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.113</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1.359</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -2652,24 +2652,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.0371</t>
+          <t>1.0287</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>0.884</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>1.197</t>
         </is>
       </c>
       <c r="F22" t="b">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>23.00421893250425</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>29.5502781176595</v>
@@ -2681,7 +2681,7 @@
         <v>11</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2693,24 +2693,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.7496</t>
+          <t>2.7903</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.150</t>
+          <t>2.181</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3.517</t>
+          <t>3.570</t>
         </is>
       </c>
       <c r="F23" t="b">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>3.072968489481465e-05</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>59.757586912448</v>
@@ -2722,7 +2722,7 @@
         <v>11</v>
       </c>
       <c r="K23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2734,17 +2734,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.8901</t>
+          <t>0.9048</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>0.641</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.256</t>
+          <t>1.278</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -2757,7 +2757,7 @@
         <v>0.007302013766864679</v>
       </c>
       <c r="I24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>11</v>
@@ -2775,17 +2775,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6.7840</t>
+          <t>6.8041</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13.227</t>
+          <t>13.267</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -3096,24 +3096,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.8423</t>
+          <t>0.8276</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.703</t>
+          <t>0.689</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.009</t>
+          <t>0.994</t>
         </is>
       </c>
       <c r="F34" t="b">
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>23.00421893250425</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>5.419749998184648e-09</v>
@@ -3125,7 +3125,7 @@
         <v>11</v>
       </c>
       <c r="K34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3154,7 +3154,7 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>3.072968489481465e-05</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3384,17 +3384,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.9773</t>
+          <t>0.9902</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>0.968</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>1.012</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7689</t>
+          <t>0.7803</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>0.880</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -3466,17 +3466,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.9362</t>
+          <t>0.9529</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.886</t>
+          <t>0.901</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.990</t>
+          <t>1.007</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -3507,17 +3507,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.9032</t>
+          <t>0.9148</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.865</t>
+          <t>0.876</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.943</t>
+          <t>0.956</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -3548,17 +3548,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.1231</t>
+          <t>1.1362</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>1.091</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.170</t>
+          <t>1.184</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -3589,17 +3589,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.1252</t>
+          <t>1.1384</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.061</t>
+          <t>1.073</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1.208</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.2331</t>
+          <t>1.2451</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.129</t>
+          <t>1.139</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.347</t>
+          <t>1.361</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.9988</t>
+          <t>1.0103</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.838</t>
+          <t>0.847</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -3712,24 +3712,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.3550</t>
+          <t>3.4186</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.392</t>
+          <t>2.435</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4.707</t>
+          <t>4.800</t>
         </is>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0002366379193354806</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -3753,17 +3753,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.5924</t>
+          <t>0.5954</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.152</t>
+          <t>1.158</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -3776,7 +3776,7 @@
         <v>0.00212863075208769</v>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>11</v>
@@ -3828,17 +3828,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.0666</t>
+          <t>1.0807</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.052</t>
+          <t>1.066</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.081</t>
+          <t>1.095</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -3869,17 +3869,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.0158</t>
+          <t>1.0309</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>0.983</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.081</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -3910,17 +3910,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.0033</t>
+          <t>1.0212</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>0.995</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.029</t>
+          <t>1.048</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.1053</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>1.092</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>1.147</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -3992,17 +3992,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.3311</t>
+          <t>1.3467</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.301</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.377</t>
+          <t>1.394</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -4033,17 +4033,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.0729</t>
+          <t>1.0854</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.001</t>
+          <t>1.013</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.150</t>
+          <t>1.163</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -4074,17 +4074,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.1090</t>
+          <t>1.1198</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.241</t>
+          <t>1.253</t>
         </is>
       </c>
       <c r="F22" t="b">
@@ -4115,24 +4115,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.3504</t>
+          <t>1.3660</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.102</t>
+          <t>1.115</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.655</t>
+          <t>1.674</t>
         </is>
       </c>
       <c r="F23" t="b">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0.000434689012210665</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -4156,17 +4156,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.0973</t>
+          <t>2.1371</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.879</t>
+          <t>2.936</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>11</v>
@@ -4197,17 +4197,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.9701</t>
+          <t>0.9749</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>0.586</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.614</t>
+          <t>1.622</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -4220,7 +4220,7 @@
         <v>0.00212863075208769</v>
       </c>
       <c r="I25" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>11</v>
@@ -4576,7 +4576,7 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.000434689012210665</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -4620,10 +4620,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0002366379193354806</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>11</v>
@@ -4664,10 +4664,10 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
@@ -4806,17 +4806,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.7333</t>
+          <t>0.7436</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>0.719</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>0.769</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -4847,24 +4847,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.6624</t>
+          <t>0.5278</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>0.438</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>0.637</t>
         </is>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1.387534855497648</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4888,17 +4888,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.7141</t>
+          <t>0.7267</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>0.673</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>0.785</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -4929,17 +4929,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.6087</t>
+          <t>0.6172</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>0.573</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>0.665</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -4970,17 +4970,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.6358</t>
+          <t>0.6433</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>0.595</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>0.695</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -5011,17 +5011,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.9609</t>
+          <t>0.9728</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.861</t>
+          <t>0.871</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>1.086</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -5052,17 +5052,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.0661</t>
+          <t>1.0787</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>0.931</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.250</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -5093,17 +5093,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.2151</t>
+          <t>1.2307</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.986</t>
+          <t>0.999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.516</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -5134,17 +5134,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.0614</t>
+          <t>1.0784</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>0.786</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1.480</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -5175,17 +5175,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.2371</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>0.839</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.802</t>
+          <t>1.825</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -5198,7 +5198,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
@@ -5250,17 +5250,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.9518</t>
+          <t>0.9653</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.940</t>
+          <t>0.953</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.964</t>
+          <t>0.978</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -5291,17 +5291,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.9224</t>
+          <t>0.9364</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.880</t>
+          <t>0.893</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.967</t>
+          <t>0.982</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -5332,17 +5332,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.8905</t>
+          <t>0.9062</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.868</t>
+          <t>0.883</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.914</t>
+          <t>0.930</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -5373,17 +5373,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.9651</t>
+          <t>0.9785</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.942</t>
+          <t>0.955</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.989</t>
+          <t>1.003</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -5414,17 +5414,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.9774</t>
+          <t>0.9889</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>0.959</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.008</t>
+          <t>1.020</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -5455,17 +5455,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.2787</t>
+          <t>1.2945</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.217</t>
+          <t>1.232</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1.360</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -5496,17 +5496,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.1065</t>
+          <t>1.1196</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>1.037</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.194</t>
+          <t>1.209</t>
         </is>
       </c>
       <c r="F22" t="b">
@@ -5537,17 +5537,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.7184</t>
+          <t>1.7405</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.507</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.983</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -5578,17 +5578,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.1782</t>
+          <t>1.1971</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>0.937</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.503</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -5619,17 +5619,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.2717</t>
+          <t>0.2749</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>0.462</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -5642,7 +5642,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>5</v>
@@ -5735,17 +5735,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.3926</t>
+          <t>1.7741</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.212</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.600</t>
+          <t>2.136</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -5755,7 +5755,7 @@
         <v>1e-10</v>
       </c>
       <c r="H29" t="n">
-        <v>1.387534855497648</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>5</v>
@@ -5764,7 +5764,7 @@
         <v>5</v>
       </c>
       <c r="K29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -6086,10 +6086,10 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
@@ -6292,7 +6292,7 @@
         <v>1.483209665604275</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
@@ -6310,24 +6310,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.1068</t>
+          <t>0.8557</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.014</t>
+          <t>0.761</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.207</t>
+          <t>0.962</t>
         </is>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.243815353255385</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>2.78265041642975</v>
@@ -6339,7 +6339,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -6392,24 +6392,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.0034</t>
+          <t>0.7499</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.906</t>
+          <t>0.650</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>0.866</t>
         </is>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>14.04027223744697</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>17.27947157290733</v>
@@ -6421,7 +6421,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6538,7 +6538,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>4</v>
@@ -6620,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>4</v>
@@ -7017,7 +7017,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.002196355696408192</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -7058,7 +7058,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002465793332856014</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -7508,7 +7508,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>4</v>
@@ -7908,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.002196355696408192</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>4</v>
@@ -7949,10 +7949,10 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.002465793332856014</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>4</v>
@@ -8158,7 +8158,7 @@
         <v>0.8169985545003832</v>
       </c>
       <c r="I5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>22</v>
@@ -8176,24 +8176,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.0776</t>
+          <t>1.0175</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.940</t>
+          <t>0.880</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.177</t>
         </is>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5592950366438387</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>1.646934490442913</v>
@@ -8205,7 +8205,7 @@
         <v>22</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -8217,24 +8217,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.2282</t>
+          <t>1.0295</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.091</t>
+          <t>0.892</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.382</t>
+          <t>1.188</t>
         </is>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>4.031118604268735</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>5.494256927154148</v>
@@ -8246,7 +8246,7 @@
         <v>22</v>
       </c>
       <c r="K7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -8258,24 +8258,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.8147</t>
+          <t>0.4738</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>0.397</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>0.565</t>
         </is>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>26.18808922765436</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>6.364320585280228</v>
@@ -8287,7 +8287,7 @@
         <v>22</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -8299,24 +8299,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.1354</t>
+          <t>1.0851</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.920</t>
+          <t>0.870</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.401</t>
+          <t>1.353</t>
         </is>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>6.140869189346068</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>22.93540666350227</v>
@@ -8328,7 +8328,7 @@
         <v>22</v>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -8363,7 +8363,7 @@
         <v>77.57227313530413</v>
       </c>
       <c r="I10" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>22</v>
@@ -8404,7 +8404,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>22</v>
@@ -8442,10 +8442,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00288422364583929</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>22</v>
@@ -8886,7 +8886,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00288422364583929</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>22</v>
@@ -9330,7 +9330,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00288422364583929</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>22</v>
@@ -9374,7 +9374,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>22</v>
@@ -9818,7 +9818,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>22</v>
@@ -10024,7 +10024,7 @@
         <v>2.885405828677026</v>
       </c>
       <c r="I5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>22</v>
@@ -10083,24 +10083,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.0807</t>
+          <t>0.5912</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.001</t>
+          <t>0.505</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>14.57663399836541</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>9.916554324692951</v>
@@ -10112,7 +10112,7 @@
         <v>22</v>
       </c>
       <c r="K7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -10124,24 +10124,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.2017</t>
+          <t>0.7504</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.080</t>
+          <t>0.624</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>0.902</t>
         </is>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>26.44161851777137</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>23.6136144234633</v>
@@ -10153,7 +10153,7 @@
         <v>22</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -10182,7 +10182,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1.072687171428666e-06</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>53.3585696487147</v>
@@ -10194,7 +10194,7 @@
         <v>22</v>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -10229,7 +10229,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>22</v>
@@ -10270,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>22</v>
@@ -10349,7 +10349,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0007096613591267564</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -10793,7 +10793,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0007096613591267564</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>22</v>
@@ -11237,10 +11237,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0007096613591267564</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>22</v>
@@ -11684,7 +11684,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>22</v>
@@ -11999,7 +11999,7 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0004117208146238172</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -12046,7 +12046,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
         <v>22</v>
@@ -12087,7 +12087,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
         <v>22</v>
@@ -12125,7 +12125,7 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0007096613591267564</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -12443,7 +12443,7 @@
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0004117208146238172</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -12490,7 +12490,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>22</v>
@@ -12531,7 +12531,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
         <v>22</v>
@@ -12887,7 +12887,7 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0004117208146238172</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -12934,7 +12934,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
         <v>22</v>
@@ -12975,7 +12975,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
         <v>22</v>
@@ -13019,7 +13019,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K85" t="b">
         <v>1</v>
@@ -13051,7 +13051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13090,6 +13090,16 @@
           <t>any_non_ok_status</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>quality_flag</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>quality_flag_detail</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13103,10 +13113,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -13117,6 +13127,10 @@
       <c r="G2" t="b">
         <v>1</v>
       </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13130,10 +13144,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -13144,6 +13158,10 @@
       <c r="G3" t="b">
         <v>1</v>
       </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13157,10 +13175,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -13171,6 +13189,14 @@
       <c r="G4" t="b">
         <v>1</v>
       </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>(1920,0,INSUFFICIENT_SIGNAL)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13184,10 +13210,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -13198,6 +13224,14 @@
       <c r="G5" t="b">
         <v>1</v>
       </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>(1920,0,INSUFFICIENT_SIGNAL)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13211,13 +13245,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -13225,6 +13259,10 @@
       <c r="G6" t="b">
         <v>1</v>
       </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13238,10 +13276,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
@@ -13252,6 +13290,10 @@
       <c r="G7" t="b">
         <v>1</v>
       </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13265,13 +13307,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -13279,6 +13321,10 @@
       <c r="G8" t="b">
         <v>1</v>
       </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13441,7 +13487,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2334</v>
+        <v>1917</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -13523,7 +13569,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>440</v>
+        <v>382</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -13605,7 +13651,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2489</v>
+        <v>2255</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -13687,7 +13733,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>8371</v>
+        <v>6969</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -13769,7 +13815,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2528</v>
+        <v>2258</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -13851,7 +13897,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>9453</v>
+        <v>8785</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -13933,7 +13979,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>14555</v>
+        <v>12331</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -14015,7 +14061,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5414</v>
+        <v>5043</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -14097,7 +14143,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2651</v>
+        <v>2437</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -14179,7 +14225,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>12719</v>
+        <v>11089</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -14261,7 +14307,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>579</v>
+        <v>536</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -14343,7 +14389,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>608</v>
+        <v>545</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -14425,7 +14471,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5502</v>
+        <v>4867</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -14507,7 +14553,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -14517,20 +14563,20 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L15" t="n">
         <v>32.43851239051246</v>
       </c>
       <c r="M15" t="n">
-        <v>32.43851239051246</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>32.43851239051246</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>32.43851239051246</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>6.875321376568033e-05</v>
@@ -14539,16 +14585,16 @@
         <v>9228367.799677702</v>
       </c>
       <c r="R15" t="n">
-        <v>0.007251476675229577</v>
+        <v>0.006244675424401279</v>
       </c>
       <c r="S15" t="n">
-        <v>0.004977099451234414</v>
+        <v>0.004148915109321112</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0003649695530582609</v>
+        <v>0.000293447367043345</v>
       </c>
       <c r="U15" t="n">
-        <v>0.004826281022820701</v>
+        <v>0.004022801299623638</v>
       </c>
       <c r="V15" t="n">
         <v>45</v>
@@ -14589,7 +14635,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -14671,7 +14717,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2777</v>
+        <v>2512</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
@@ -14753,7 +14799,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
@@ -14763,20 +14809,20 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L18" t="n">
         <v>7.452380656070012e-05</v>
       </c>
       <c r="M18" t="n">
-        <v>7.452380656070012e-05</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>7.452380656070012e-05</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>7.452380656070012e-05</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>1.005963912815686e-05</v>
@@ -14785,16 +14831,16 @@
         <v>6118358.527714487</v>
       </c>
       <c r="R18" t="n">
-        <v>0.002711055426802172</v>
+        <v>0.00271105502540093</v>
       </c>
       <c r="S18" t="n">
-        <v>0.001870934864285735</v>
+        <v>0.001870934524209368</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0002630359486540559</v>
+        <v>0.000263035789243688</v>
       </c>
       <c r="U18" t="n">
-        <v>0.001813193052600191</v>
+        <v>0.001813192725007606</v>
       </c>
       <c r="V18" t="n">
         <v>45</v>
@@ -14835,7 +14881,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -14845,20 +14891,20 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>0.0004379764066248792</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0004379764066248792</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0004379764066248792</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0004379764066248792</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>2.329822333850928e-05</v>
@@ -14867,16 +14913,16 @@
         <v>12454797.82948834</v>
       </c>
       <c r="R19" t="n">
-        <v>0.002233170341998427</v>
+        <v>0.002233168758372485</v>
       </c>
       <c r="S19" t="n">
-        <v>0.001515099856072471</v>
+        <v>0.001515098495823728</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0002351676271659837</v>
+        <v>0.0002351665140155682</v>
       </c>
       <c r="U19" t="n">
-        <v>0.001467479519362523</v>
+        <v>0.001467478219270512</v>
       </c>
       <c r="V19" t="n">
         <v>45</v>
@@ -14917,7 +14963,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1019</v>
+        <v>924</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -14997,7 +15043,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I21" t="b">
         <v>1</v>
@@ -15007,11 +15053,11 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>insufficient_signal</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.0005314895659107588</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -15077,7 +15123,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -15157,7 +15203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -15238,11 +15284,9 @@
           <t>theta_estimation_windows</t>
         </is>
       </c>
-      <c r="H24" t="n">
-        <v>6</v>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -15315,7 +15359,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I25" t="b">
         <v>1</v>
@@ -15325,11 +15369,11 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.001732276136594185</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -15343,9 +15387,7 @@
       <c r="P25" t="n">
         <v>1.058915508815279e-05</v>
       </c>
-      <c r="Q25" t="n">
-        <v>10700952.67297973</v>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
         <v>0.001394903326141745</v>
       </c>
@@ -15397,7 +15439,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -15478,11 +15520,9 @@
           <t>theta_estimation_windows</t>
         </is>
       </c>
-      <c r="H27" t="n">
-        <v>5</v>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -15554,11 +15594,9 @@
           <t>theta_estimation_windows</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>6</v>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -15612,10 +15650,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D29" t="n">
+        <v>-2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -15631,7 +15667,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>47859</v>
+        <v>41155</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -15694,10 +15730,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D30" t="n">
+        <v>-2</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -15713,7 +15747,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>9213</v>
+        <v>8453</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -15776,10 +15810,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D31" t="n">
+        <v>-2</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -15795,7 +15827,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>15543</v>
+        <v>14337</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -15877,7 +15909,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1917</v>
+        <v>1614</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -15959,7 +15991,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>319</v>
+        <v>271</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -16041,7 +16073,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2997</v>
+        <v>2669</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -16123,7 +16155,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6214</v>
+        <v>5357</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -16205,7 +16237,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1451</v>
+        <v>1317</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
@@ -16287,7 +16319,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>12335</v>
+        <v>11337</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -16369,7 +16401,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>8300</v>
+        <v>7226</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
@@ -16451,7 +16483,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>4245</v>
+        <v>3928</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -16533,7 +16565,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>9253</v>
+        <v>8656</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -16615,7 +16647,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>7177</v>
+        <v>6311</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
@@ -16697,7 +16729,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>4696</v>
+        <v>4440</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
@@ -16779,7 +16811,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1559</v>
+        <v>1419</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -16861,7 +16893,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3826</v>
+        <v>3429</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -16943,7 +16975,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1436</v>
+        <v>1360</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -17025,7 +17057,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>432</v>
+        <v>400</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
@@ -17107,7 +17139,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2319</v>
+        <v>2116</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -17189,7 +17221,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -17271,7 +17303,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -17281,20 +17313,20 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L49" t="n">
         <v>23.00421893250425</v>
       </c>
       <c r="M49" t="n">
-        <v>23.00421893250425</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>23.00421893250425</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>23.00421893250425</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>2.863811202493094e-05</v>
@@ -17303,16 +17335,16 @@
         <v>6356731.875954096</v>
       </c>
       <c r="R49" t="n">
-        <v>0.002569092699904312</v>
+        <v>0.002461988004018048</v>
       </c>
       <c r="S49" t="n">
-        <v>0.001835155190946343</v>
+        <v>0.00174370606003249</v>
       </c>
       <c r="T49" t="n">
-        <v>0.0001258025307869374</v>
+        <v>6.910020417332571e-05</v>
       </c>
       <c r="U49" t="n">
-        <v>0.001810495176130975</v>
+        <v>0.001720646926298613</v>
       </c>
       <c r="V49" t="n">
         <v>45</v>
@@ -17353,7 +17385,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>935</v>
+        <v>855</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
@@ -17435,7 +17467,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
@@ -17515,7 +17547,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -17525,20 +17557,20 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L52" t="n">
         <v>3.072968489481465e-05</v>
       </c>
       <c r="M52" t="n">
-        <v>3.072968489481465e-05</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.072968489481465e-05</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.072968489481465e-05</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
         <v>6.818459915783816e-06</v>
@@ -17547,16 +17579,16 @@
         <v>3228260.937217557</v>
       </c>
       <c r="R52" t="n">
-        <v>0.001541102012171131</v>
+        <v>0.001541101957002432</v>
       </c>
       <c r="S52" t="n">
-        <v>0.001114994142800079</v>
+        <v>0.001114994095514668</v>
       </c>
       <c r="T52" t="n">
-        <v>7.221380949936447e-05</v>
+        <v>7.22137938847468e-05</v>
       </c>
       <c r="U52" t="n">
-        <v>0.001100036625283164</v>
+        <v>0.001100036578819179</v>
       </c>
       <c r="V52" t="n">
         <v>45</v>
@@ -17597,7 +17629,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>365</v>
+        <v>340</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
@@ -17678,11 +17710,9 @@
           <t>theta_estimation_windows</t>
         </is>
       </c>
-      <c r="H54" t="n">
-        <v>13</v>
-      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
@@ -17755,7 +17785,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I55" t="b">
         <v>1</v>
@@ -17765,11 +17795,11 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>insufficient_signal</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>99.99953689966499</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -17783,9 +17813,7 @@
       <c r="P55" t="n">
         <v>1.640139550268365e-05</v>
       </c>
-      <c r="Q55" t="n">
-        <v>12379053.03798892</v>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="n">
         <v>0.001304725494108278</v>
       </c>
@@ -17837,7 +17865,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="I56" t="b">
         <v>0</v>
@@ -17918,11 +17946,9 @@
           <t>theta_estimation_windows</t>
         </is>
       </c>
-      <c r="H57" t="n">
-        <v>7</v>
-      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
@@ -17994,11 +18020,9 @@
           <t>theta_estimation_windows</t>
         </is>
       </c>
-      <c r="H58" t="n">
-        <v>11</v>
-      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
@@ -18052,10 +18076,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D59" t="n">
+        <v>-2</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -18071,7 +18093,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>31244</v>
+        <v>27428</v>
       </c>
       <c r="I59" t="b">
         <v>0</v>
@@ -18134,10 +18156,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D60" t="n">
+        <v>-2</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -18153,7 +18173,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>12618</v>
+        <v>11761</v>
       </c>
       <c r="I60" t="b">
         <v>0</v>
@@ -18216,10 +18236,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D61" t="n">
+        <v>-2</v>
       </c>
       <c r="E61" t="n">
         <v>2</v>
@@ -18235,7 +18253,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>26869</v>
+        <v>24754</v>
       </c>
       <c r="I61" t="b">
         <v>0</v>
@@ -19959,20 +19977,20 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L82" t="n">
         <v>0.000434689012210665</v>
       </c>
       <c r="M82" t="n">
-        <v>0.000434689012210665</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>0.000434689012210665</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>0.000434689012210665</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
         <v>1.73715714647134e-05</v>
@@ -19981,16 +19999,16 @@
         <v>3839877.922342301</v>
       </c>
       <c r="R82" t="n">
-        <v>0.001681902417772995</v>
+        <v>0.001681901556966151</v>
       </c>
       <c r="S82" t="n">
-        <v>0.001077063353686314</v>
+        <v>0.001077062699508534</v>
       </c>
       <c r="T82" t="n">
-        <v>4.106638746835924e-05</v>
+        <v>4.106638782768162e-05</v>
       </c>
       <c r="U82" t="n">
-        <v>0.001127647796106822</v>
+        <v>0.001127647111531467</v>
       </c>
       <c r="V82" t="n">
         <v>41</v>
@@ -20121,20 +20139,20 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L84" t="n">
         <v>0.0002366379193354806</v>
       </c>
       <c r="M84" t="n">
-        <v>0.0002366379193354806</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0.0002366379193354806</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>0.0002366379193354806</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
         <v>1.800391074327346e-06</v>
@@ -20143,16 +20161,16 @@
         <v>1208163.875948411</v>
       </c>
       <c r="R84" t="n">
-        <v>0.0006156452590260541</v>
+        <v>0.0006156451935960946</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0004222876250692952</v>
+        <v>0.0004222875727868902</v>
       </c>
       <c r="T84" t="n">
-        <v>0.0001034634170479926</v>
+        <v>0.0001034633904681415</v>
       </c>
       <c r="U84" t="n">
-        <v>0.000440456643395658</v>
+        <v>0.0004404565894958253</v>
       </c>
       <c r="V84" t="n">
         <v>41</v>
@@ -20203,11 +20221,11 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.01850289296067031</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -20221,9 +20239,7 @@
       <c r="P85" t="n">
         <v>7.26395769522143e-06</v>
       </c>
-      <c r="Q85" t="n">
-        <v>6108913.735075328</v>
-      </c>
+      <c r="Q85" t="inlineStr"/>
       <c r="R85" t="n">
         <v>0.001183755634280908</v>
       </c>
@@ -20367,11 +20383,11 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>insufficient_signal</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>99.3020403130092</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -20447,11 +20463,11 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>insufficient_signal</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>5.711663740193273e-05</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -20498,10 +20514,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D89" t="n">
+        <v>-2</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -20580,10 +20594,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D90" t="n">
+        <v>-2</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -20662,10 +20674,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D91" t="n">
+        <v>-2</v>
       </c>
       <c r="E91" t="n">
         <v>2</v>
@@ -20853,20 +20863,20 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L93" t="n">
         <v>1.387534855497648</v>
       </c>
       <c r="M93" t="n">
-        <v>1.387534855497648</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1.387534855497648</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>1.387534855497648</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
         <v>0.01080369840244792</v>
@@ -20875,16 +20885,16 @@
         <v>2441937320.858485</v>
       </c>
       <c r="R93" t="n">
-        <v>0.9669730835446488</v>
+        <v>0.5717449709388923</v>
       </c>
       <c r="S93" t="n">
-        <v>0.5164832053648063</v>
+        <v>0.2649250967086366</v>
       </c>
       <c r="T93" t="n">
-        <v>0.2254789904490457</v>
+        <v>0.02472159860974266</v>
       </c>
       <c r="U93" t="n">
-        <v>0.6360070460252275</v>
+        <v>0.330806102792235</v>
       </c>
       <c r="V93" t="n">
         <v>35</v>
@@ -22807,11 +22817,11 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0.00090135976358241</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
@@ -22825,9 +22835,7 @@
       <c r="P117" t="n">
         <v>2.374017766628377e-06</v>
       </c>
-      <c r="Q117" t="n">
-        <v>1726566.273832771</v>
-      </c>
+      <c r="Q117" t="inlineStr"/>
       <c r="R117" t="n">
         <v>0.0003282085913929571</v>
       </c>
@@ -22889,11 +22897,11 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>insufficient_signal</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>99.99990329729533</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
@@ -22940,10 +22948,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D119" t="n">
+        <v>-2</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -23022,10 +23028,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D120" t="n">
+        <v>-2</v>
       </c>
       <c r="E120" t="n">
         <v>1</v>
@@ -23104,10 +23108,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D121" t="n">
+        <v>-2</v>
       </c>
       <c r="E121" t="n">
         <v>2</v>
@@ -23205,7 +23207,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>909</v>
+        <v>646</v>
       </c>
       <c r="I122" t="b">
         <v>0</v>
@@ -23287,21 +23289,21 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J123" t="b">
         <v>0</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>insufficient_signal</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>5.022565752920349e-11</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
@@ -23367,7 +23369,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>510</v>
+        <v>380</v>
       </c>
       <c r="I124" t="b">
         <v>0</v>
@@ -23449,7 +23451,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>2096</v>
+        <v>1757</v>
       </c>
       <c r="I125" t="b">
         <v>0</v>
@@ -23531,7 +23533,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>2989</v>
+        <v>2286</v>
       </c>
       <c r="I126" t="b">
         <v>0</v>
@@ -23613,7 +23615,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="I127" t="b">
         <v>0</v>
@@ -23623,20 +23625,20 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L127" t="n">
         <v>2.243815353255385</v>
       </c>
       <c r="M127" t="n">
-        <v>2.243815353255385</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.243815353255385</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>2.243815353255385</v>
+        <v>0</v>
       </c>
       <c r="P127" t="n">
         <v>0.005773456509171279</v>
@@ -23645,16 +23647,16 @@
         <v>507297577.4677144</v>
       </c>
       <c r="R127" t="n">
-        <v>0.4304533022041161</v>
+        <v>0.2826010687715073</v>
       </c>
       <c r="S127" t="n">
-        <v>0.2347127166959212</v>
+        <v>0.1374563670893023</v>
       </c>
       <c r="T127" t="n">
-        <v>0.04750305605191918</v>
+        <v>0.01717432812372377</v>
       </c>
       <c r="U127" t="n">
-        <v>0.3695310337909884</v>
+        <v>0.2166234173672448</v>
       </c>
       <c r="V127" t="n">
         <v>34</v>
@@ -23695,7 +23697,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2270</v>
+        <v>1798</v>
       </c>
       <c r="I128" t="b">
         <v>0</v>
@@ -23777,7 +23779,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>9846</v>
+        <v>8681</v>
       </c>
       <c r="I129" t="b">
         <v>0</v>
@@ -23859,7 +23861,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>3383</v>
+        <v>2659</v>
       </c>
       <c r="I130" t="b">
         <v>0</v>
@@ -23941,7 +23943,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="I131" t="b">
         <v>0</v>
@@ -24023,7 +24025,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>2930</v>
+        <v>2396</v>
       </c>
       <c r="I132" t="b">
         <v>0</v>
@@ -24105,7 +24107,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>10316</v>
+        <v>9308</v>
       </c>
       <c r="I133" t="b">
         <v>0</v>
@@ -24187,7 +24189,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>2616</v>
+        <v>2105</v>
       </c>
       <c r="I134" t="b">
         <v>0</v>
@@ -24269,7 +24271,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="I135" t="b">
         <v>0</v>
@@ -24279,20 +24281,20 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L135" t="n">
         <v>14.04027223744697</v>
       </c>
       <c r="M135" t="n">
-        <v>14.04027223744697</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>14.04027223744697</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>14.04027223744697</v>
+        <v>0</v>
       </c>
       <c r="P135" t="n">
         <v>0.001233959627050319</v>
@@ -24301,16 +24303,16 @@
         <v>146651610.0747123</v>
       </c>
       <c r="R135" t="n">
-        <v>0.08086813664592545</v>
+        <v>0.05025891464825721</v>
       </c>
       <c r="S135" t="n">
-        <v>0.0454772365011845</v>
+        <v>0.02486624396341348</v>
       </c>
       <c r="T135" t="n">
-        <v>0.01200181973318842</v>
+        <v>0.003351778973384352</v>
       </c>
       <c r="U135" t="n">
-        <v>0.07138965181033778</v>
+        <v>0.03919710472933705</v>
       </c>
       <c r="V135" t="n">
         <v>34</v>
@@ -24351,7 +24353,7 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>2231</v>
+        <v>1881</v>
       </c>
       <c r="I136" t="b">
         <v>0</v>
@@ -24433,7 +24435,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>5341</v>
+        <v>4839</v>
       </c>
       <c r="I137" t="b">
         <v>0</v>
@@ -24515,7 +24517,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>1432</v>
+        <v>1217</v>
       </c>
       <c r="I138" t="b">
         <v>0</v>
@@ -24597,7 +24599,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I139" t="b">
         <v>0</v>
@@ -24677,7 +24679,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>1145</v>
+        <v>985</v>
       </c>
       <c r="I140" t="b">
         <v>0</v>
@@ -24759,7 +24761,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>1748</v>
+        <v>1579</v>
       </c>
       <c r="I141" t="b">
         <v>0</v>
@@ -24841,7 +24843,7 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>798</v>
+        <v>667</v>
       </c>
       <c r="I142" t="b">
         <v>0</v>
@@ -24921,7 +24923,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I143" t="b">
         <v>0</v>
@@ -25001,7 +25003,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>665</v>
+        <v>588</v>
       </c>
       <c r="I144" t="b">
         <v>0</v>
@@ -25081,7 +25083,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>735</v>
+        <v>676</v>
       </c>
       <c r="I145" t="b">
         <v>0</v>
@@ -25163,7 +25165,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>382</v>
+        <v>328</v>
       </c>
       <c r="I146" t="b">
         <v>0</v>
@@ -25243,7 +25245,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I147" t="b">
         <v>1</v>
@@ -25253,11 +25255,11 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>insufficient_signal</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>99.99999836563993</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -25323,7 +25325,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="I148" t="b">
         <v>0</v>
@@ -25405,7 +25407,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="I149" t="b">
         <v>0</v>
@@ -25487,7 +25489,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="I150" t="b">
         <v>0</v>
@@ -25566,11 +25568,9 @@
           <t>theta_estimation_windows</t>
         </is>
       </c>
-      <c r="H151" t="n">
-        <v>8</v>
-      </c>
+      <c r="H151" t="inlineStr"/>
       <c r="I151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J151" t="b">
         <v>0</v>
@@ -25643,7 +25643,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="I152" t="b">
         <v>0</v>
@@ -25653,20 +25653,20 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L152" t="n">
         <v>0.002196355696408192</v>
       </c>
       <c r="M152" t="n">
-        <v>0.002196355696408192</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>0.002196355696408192</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>0.002196355696408192</v>
+        <v>0</v>
       </c>
       <c r="P152" t="n">
         <v>4.489404642949655e-06</v>
@@ -25675,16 +25675,16 @@
         <v>773711.3954322882</v>
       </c>
       <c r="R152" t="n">
-        <v>0.0004735899327455301</v>
+        <v>0.000473589617175287</v>
       </c>
       <c r="S152" t="n">
-        <v>0.0002549159279558861</v>
+        <v>0.0002549157214679891</v>
       </c>
       <c r="T152" t="n">
-        <v>3.332908565272732e-05</v>
+        <v>3.332906573717898e-05</v>
       </c>
       <c r="U152" t="n">
-        <v>0.0004019487411486633</v>
+        <v>0.0004019484121293635</v>
       </c>
       <c r="V152" t="n">
         <v>34</v>
@@ -25725,7 +25725,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I153" t="b">
         <v>0</v>
@@ -25805,7 +25805,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="I154" t="b">
         <v>0</v>
@@ -25885,7 +25885,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I155" t="b">
         <v>1</v>
@@ -25895,11 +25895,11 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>insufficient_signal</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>99.99990960012552</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
         <v>0</v>
@@ -25965,7 +25965,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="I156" t="b">
         <v>0</v>
@@ -25975,20 +25975,20 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L156" t="n">
         <v>0.002465793332856014</v>
       </c>
       <c r="M156" t="n">
-        <v>0.002465793332856014</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>0.002465793332856014</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
-        <v>0.002465793332856014</v>
+        <v>0</v>
       </c>
       <c r="P156" t="n">
         <v>3.124354048655279e-06</v>
@@ -25997,16 +25997,16 @@
         <v>1192894.336522422</v>
       </c>
       <c r="R156" t="n">
-        <v>0.0002682187803388948</v>
+        <v>0.0002682186685768958</v>
       </c>
       <c r="S156" t="n">
-        <v>0.0001388365966771013</v>
+        <v>0.0001388365228440479</v>
       </c>
       <c r="T156" t="n">
-        <v>6.185220709144126e-06</v>
+        <v>6.185230687773648e-06</v>
       </c>
       <c r="U156" t="n">
-        <v>0.000219290023999888</v>
+        <v>0.0002192899070382615</v>
       </c>
       <c r="V156" t="n">
         <v>34</v>
@@ -26047,7 +26047,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I157" t="b">
         <v>1</v>
@@ -26057,11 +26057,11 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.201112079782786</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
         <v>0</v>
@@ -26075,9 +26075,7 @@
       <c r="P157" t="n">
         <v>5.672950653047245e-06</v>
       </c>
-      <c r="Q157" t="n">
-        <v>4608526.005304292</v>
-      </c>
+      <c r="Q157" t="inlineStr"/>
       <c r="R157" t="n">
         <v>0.0003874501427048034</v>
       </c>
@@ -26110,10 +26108,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D158" t="n">
+        <v>-2</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
@@ -26129,7 +26125,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>12751</v>
+        <v>10116</v>
       </c>
       <c r="I158" t="b">
         <v>0</v>
@@ -26192,10 +26188,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D159" t="n">
+        <v>-2</v>
       </c>
       <c r="E159" t="n">
         <v>1</v>
@@ -26211,7 +26205,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>695</v>
+        <v>546</v>
       </c>
       <c r="I159" t="b">
         <v>0</v>
@@ -26274,10 +26268,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D160" t="n">
+        <v>-2</v>
       </c>
       <c r="E160" t="n">
         <v>2</v>
@@ -26293,7 +26285,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>10156</v>
+        <v>8394</v>
       </c>
       <c r="I160" t="b">
         <v>0</v>
@@ -26356,10 +26348,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D161" t="n">
+        <v>-2</v>
       </c>
       <c r="E161" t="n">
         <v>3</v>
@@ -26375,7 +26365,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>30332</v>
+        <v>27064</v>
       </c>
       <c r="I161" t="b">
         <v>0</v>
@@ -26457,7 +26447,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>634</v>
+        <v>493</v>
       </c>
       <c r="I162" t="b">
         <v>0</v>
@@ -26539,7 +26529,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I163" t="b">
         <v>1</v>
@@ -26549,11 +26539,11 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1.626722517030997</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
@@ -26567,9 +26557,7 @@
       <c r="P163" t="n">
         <v>0.007230280099094124</v>
       </c>
-      <c r="Q163" t="n">
-        <v>3545666616.544322</v>
-      </c>
+      <c r="Q163" t="inlineStr"/>
       <c r="R163" t="n">
         <v>0.2482861974725662</v>
       </c>
@@ -26621,7 +26609,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>354</v>
+        <v>290</v>
       </c>
       <c r="I164" t="b">
         <v>0</v>
@@ -26703,7 +26691,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>1863</v>
+        <v>1510</v>
       </c>
       <c r="I165" t="b">
         <v>0</v>
@@ -26785,7 +26773,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>2288</v>
+        <v>1860</v>
       </c>
       <c r="I166" t="b">
         <v>0</v>
@@ -26867,7 +26855,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="I167" t="b">
         <v>0</v>
@@ -26877,20 +26865,20 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L167" t="n">
         <v>0.5592950366438387</v>
       </c>
       <c r="M167" t="n">
-        <v>0.5592950366438387</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>0.5592950366438387</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
-        <v>0.5592950366438387</v>
+        <v>0</v>
       </c>
       <c r="P167" t="n">
         <v>0.003554301829760449</v>
@@ -26899,16 +26887,16 @@
         <v>909929765.0024439</v>
       </c>
       <c r="R167" t="n">
-        <v>0.2347223613623552</v>
+        <v>0.2181656903485621</v>
       </c>
       <c r="S167" t="n">
-        <v>0.1041747407728661</v>
+        <v>0.09467867640102026</v>
       </c>
       <c r="T167" t="n">
-        <v>0.01280970618460506</v>
+        <v>0.01526740574002383</v>
       </c>
       <c r="U167" t="n">
-        <v>0.2269635663914041</v>
+        <v>0.2057614510071569</v>
       </c>
       <c r="V167" t="n">
         <v>30</v>
@@ -26949,7 +26937,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>1596</v>
+        <v>1315</v>
       </c>
       <c r="I168" t="b">
         <v>0</v>
@@ -27031,7 +27019,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>8978</v>
+        <v>7708</v>
       </c>
       <c r="I169" t="b">
         <v>0</v>
@@ -27113,7 +27101,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>2711</v>
+        <v>2215</v>
       </c>
       <c r="I170" t="b">
         <v>0</v>
@@ -27195,7 +27183,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="I171" t="b">
         <v>0</v>
@@ -27205,20 +27193,20 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L171" t="n">
         <v>4.031118604268735</v>
       </c>
       <c r="M171" t="n">
-        <v>4.031118604268735</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>4.031118604268735</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
-        <v>4.031118604268735</v>
+        <v>0</v>
       </c>
       <c r="P171" t="n">
         <v>0.001620102997263858</v>
@@ -27227,16 +27215,16 @@
         <v>339042003.6688085</v>
       </c>
       <c r="R171" t="n">
-        <v>0.1116895599656951</v>
+        <v>0.08948344240889723</v>
       </c>
       <c r="S171" t="n">
-        <v>0.05167768574235382</v>
+        <v>0.03848171836962441</v>
       </c>
       <c r="T171" t="n">
-        <v>0.005545007761226212</v>
+        <v>0.007086997426987249</v>
       </c>
       <c r="U171" t="n">
-        <v>0.1125609546515694</v>
+        <v>0.0835070149127278</v>
       </c>
       <c r="V171" t="n">
         <v>30</v>
@@ -27277,7 +27265,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>2153</v>
+        <v>1805</v>
       </c>
       <c r="I172" t="b">
         <v>0</v>
@@ -27359,7 +27347,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>9813</v>
+        <v>8519</v>
       </c>
       <c r="I173" t="b">
         <v>0</v>
@@ -27441,7 +27429,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>2074</v>
+        <v>1769</v>
       </c>
       <c r="I174" t="b">
         <v>0</v>
@@ -27523,7 +27511,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="I175" t="b">
         <v>0</v>
@@ -27533,20 +27521,20 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L175" t="n">
         <v>26.18808922765436</v>
       </c>
       <c r="M175" t="n">
-        <v>26.18808922765436</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>26.18808922765436</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
-        <v>26.18808922765436</v>
+        <v>0</v>
       </c>
       <c r="P175" t="n">
         <v>0.001509887951077916</v>
@@ -27555,16 +27543,16 @@
         <v>138135094.2530908</v>
       </c>
       <c r="R175" t="n">
-        <v>0.08722585021731771</v>
+        <v>0.04225964643333655</v>
       </c>
       <c r="S175" t="n">
-        <v>0.04588156384844162</v>
+        <v>0.01720117896667793</v>
       </c>
       <c r="T175" t="n">
-        <v>0.0197007944807433</v>
+        <v>0.004382206090287426</v>
       </c>
       <c r="U175" t="n">
-        <v>0.09814790438342906</v>
+        <v>0.03716675837340962</v>
       </c>
       <c r="V175" t="n">
         <v>30</v>
@@ -27605,7 +27593,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>1676</v>
+        <v>1438</v>
       </c>
       <c r="I176" t="b">
         <v>0</v>
@@ -27687,7 +27675,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>5156</v>
+        <v>4484</v>
       </c>
       <c r="I177" t="b">
         <v>0</v>
@@ -27769,7 +27757,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>1205</v>
+        <v>1024</v>
       </c>
       <c r="I178" t="b">
         <v>0</v>
@@ -27851,7 +27839,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I179" t="b">
         <v>0</v>
@@ -27861,20 +27849,20 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L179" t="n">
         <v>6.140869189346068</v>
       </c>
       <c r="M179" t="n">
-        <v>6.140869189346068</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>6.140869189346068</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
-        <v>6.140869189346068</v>
+        <v>0</v>
       </c>
       <c r="P179" t="n">
         <v>0.0002495848069056586</v>
@@ -27883,16 +27871,16 @@
         <v>91200388.5661103</v>
       </c>
       <c r="R179" t="n">
-        <v>0.0165160640510957</v>
+        <v>0.01559496481646438</v>
       </c>
       <c r="S179" t="n">
-        <v>0.007349891153684123</v>
+        <v>0.006825975471749728</v>
       </c>
       <c r="T179" t="n">
-        <v>0.001224791369707448</v>
+        <v>0.001478458954591068</v>
       </c>
       <c r="U179" t="n">
-        <v>0.01599698931786179</v>
+        <v>0.01482417957741882</v>
       </c>
       <c r="V179" t="n">
         <v>30</v>
@@ -27933,7 +27921,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>885</v>
+        <v>758</v>
       </c>
       <c r="I180" t="b">
         <v>0</v>
@@ -28015,7 +28003,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>1730</v>
+        <v>1535</v>
       </c>
       <c r="I181" t="b">
         <v>0</v>
@@ -28097,7 +28085,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>689</v>
+        <v>581</v>
       </c>
       <c r="I182" t="b">
         <v>0</v>
@@ -28179,7 +28167,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I183" t="b">
         <v>1</v>
@@ -28189,11 +28177,11 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>66.52501115035452</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
         <v>0</v>
@@ -28207,9 +28195,7 @@
       <c r="P183" t="n">
         <v>0.0001218610454203461</v>
       </c>
-      <c r="Q183" t="n">
-        <v>57445095.0032995</v>
-      </c>
+      <c r="Q183" t="inlineStr"/>
       <c r="R183" t="n">
         <v>0.006066437634114253</v>
       </c>
@@ -28261,7 +28247,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>509</v>
+        <v>449</v>
       </c>
       <c r="I184" t="b">
         <v>0</v>
@@ -28343,7 +28329,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>771</v>
+        <v>682</v>
       </c>
       <c r="I185" t="b">
         <v>0</v>
@@ -28425,7 +28411,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>332</v>
+        <v>278</v>
       </c>
       <c r="I186" t="b">
         <v>0</v>
@@ -28505,7 +28491,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I187" t="b">
         <v>1</v>
@@ -28515,11 +28501,11 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>7.977790900766044e-10</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
         <v>0</v>
@@ -28533,9 +28519,7 @@
       <c r="P187" t="n">
         <v>1.771348496724364e-05</v>
       </c>
-      <c r="Q187" t="n">
-        <v>13037871.53283206</v>
-      </c>
+      <c r="Q187" t="inlineStr"/>
       <c r="R187" t="n">
         <v>0.002450475769475291</v>
       </c>
@@ -28587,7 +28571,7 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="I188" t="b">
         <v>0</v>
@@ -28667,7 +28651,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="I189" t="b">
         <v>0</v>
@@ -28749,7 +28733,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="I190" t="b">
         <v>0</v>
@@ -28759,20 +28743,20 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L190" t="n">
         <v>0.00288422364583929</v>
       </c>
       <c r="M190" t="n">
-        <v>0.00288422364583929</v>
+        <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>0.00288422364583929</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
-        <v>0.00288422364583929</v>
+        <v>0</v>
       </c>
       <c r="P190" t="n">
         <v>9.346219986368667e-06</v>
@@ -28781,16 +28765,16 @@
         <v>1845653.628095963</v>
       </c>
       <c r="R190" t="n">
-        <v>0.0006553364817021637</v>
+        <v>0.0006553357396874744</v>
       </c>
       <c r="S190" t="n">
-        <v>0.0002966508070898556</v>
+        <v>0.0002966503510992636</v>
       </c>
       <c r="T190" t="n">
-        <v>1.975628675543321e-05</v>
+        <v>1.975635624920939e-05</v>
       </c>
       <c r="U190" t="n">
-        <v>0.0006471670489594114</v>
+        <v>0.0006471660438861164</v>
       </c>
       <c r="V190" t="n">
         <v>30</v>
@@ -28831,7 +28815,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I191" t="b">
         <v>1</v>
@@ -28841,11 +28825,11 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>insufficient_signal</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>99.99999059228089</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
         <v>0</v>
@@ -28911,7 +28895,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="I192" t="b">
         <v>0</v>
@@ -28991,7 +28975,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="I193" t="b">
         <v>0</v>
@@ -29073,7 +29057,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="I194" t="b">
         <v>0</v>
@@ -29152,11 +29136,9 @@
           <t>theta_estimation_windows</t>
         </is>
       </c>
-      <c r="H195" t="n">
-        <v>4</v>
-      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J195" t="b">
         <v>0</v>
@@ -29229,7 +29211,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I196" t="b">
         <v>0</v>
@@ -29311,7 +29293,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I197" t="b">
         <v>1</v>
@@ -29321,11 +29303,11 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0.0001991363405811075</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
         <v>0</v>
@@ -29339,9 +29321,7 @@
       <c r="P197" t="n">
         <v>3.261191181183819e-06</v>
       </c>
-      <c r="Q197" t="n">
-        <v>2152306.443547339</v>
-      </c>
+      <c r="Q197" t="inlineStr"/>
       <c r="R197" t="n">
         <v>0.0002541429282926018</v>
       </c>
@@ -29374,10 +29354,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D198" t="n">
+        <v>-2</v>
       </c>
       <c r="E198" t="n">
         <v>0</v>
@@ -29393,7 +29371,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>10141</v>
+        <v>8401</v>
       </c>
       <c r="I198" t="b">
         <v>0</v>
@@ -29456,10 +29434,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D199" t="n">
+        <v>-2</v>
       </c>
       <c r="E199" t="n">
         <v>1</v>
@@ -29475,7 +29451,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>381</v>
+        <v>305</v>
       </c>
       <c r="I199" t="b">
         <v>0</v>
@@ -29538,10 +29514,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D200" t="n">
+        <v>-2</v>
       </c>
       <c r="E200" t="n">
         <v>2</v>
@@ -29557,7 +29531,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>7523</v>
+        <v>6356</v>
       </c>
       <c r="I200" t="b">
         <v>0</v>
@@ -29620,10 +29594,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D201" t="n">
+        <v>-2</v>
       </c>
       <c r="E201" t="n">
         <v>3</v>
@@ -29639,7 +29611,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>28574</v>
+        <v>24669</v>
       </c>
       <c r="I201" t="b">
         <v>0</v>
@@ -29721,7 +29693,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>665</v>
+        <v>483</v>
       </c>
       <c r="I202" t="b">
         <v>0</v>
@@ -29803,7 +29775,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I203" t="b">
         <v>1</v>
@@ -29813,11 +29785,11 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1e-10</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
         <v>0</v>
@@ -29831,9 +29803,7 @@
       <c r="P203" t="n">
         <v>0.00306251302335221</v>
       </c>
-      <c r="Q203" t="n">
-        <v>2035133059.299931</v>
-      </c>
+      <c r="Q203" t="inlineStr"/>
       <c r="R203" t="n">
         <v>0.178432089117651</v>
       </c>
@@ -29885,7 +29855,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="I204" t="b">
         <v>0</v>
@@ -29967,7 +29937,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>1236</v>
+        <v>933</v>
       </c>
       <c r="I205" t="b">
         <v>0</v>
@@ -30049,7 +30019,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>774</v>
+        <v>622</v>
       </c>
       <c r="I206" t="b">
         <v>0</v>
@@ -30131,7 +30101,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>2356</v>
+        <v>1826</v>
       </c>
       <c r="I207" t="b">
         <v>0</v>
@@ -30213,7 +30183,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="I208" t="b">
         <v>0</v>
@@ -30295,7 +30265,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>1504</v>
+        <v>1186</v>
       </c>
       <c r="I209" t="b">
         <v>0</v>
@@ -30377,7 +30347,7 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>6429</v>
+        <v>5170</v>
       </c>
       <c r="I210" t="b">
         <v>0</v>
@@ -30459,7 +30429,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>3254</v>
+        <v>2688</v>
       </c>
       <c r="I211" t="b">
         <v>0</v>
@@ -30541,7 +30511,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>2736</v>
+        <v>2199</v>
       </c>
       <c r="I212" t="b">
         <v>0</v>
@@ -30623,7 +30593,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="I213" t="b">
         <v>0</v>
@@ -30633,20 +30603,20 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L213" t="n">
         <v>14.57663399836541</v>
       </c>
       <c r="M213" t="n">
-        <v>14.57663399836541</v>
+        <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>14.57663399836541</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
-        <v>14.57663399836541</v>
+        <v>0</v>
       </c>
       <c r="P213" t="n">
         <v>0.002903570907414179</v>
@@ -30655,16 +30625,16 @@
         <v>276432660.6917195</v>
       </c>
       <c r="R213" t="n">
-        <v>0.1132358046746691</v>
+        <v>0.06146846603666596</v>
       </c>
       <c r="S213" t="n">
-        <v>0.07508950557847907</v>
+        <v>0.02803844403196465</v>
       </c>
       <c r="T213" t="n">
-        <v>0.02753761951921951</v>
+        <v>0.008361680583263286</v>
       </c>
       <c r="U213" t="n">
-        <v>0.2091946234904272</v>
+        <v>0.07934200129271068</v>
       </c>
       <c r="V213" t="n">
         <v>30</v>
@@ -30705,7 +30675,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>2025</v>
+        <v>1636</v>
       </c>
       <c r="I214" t="b">
         <v>0</v>
@@ -30787,7 +30757,7 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>7471</v>
+        <v>6185</v>
       </c>
       <c r="I215" t="b">
         <v>0</v>
@@ -30869,7 +30839,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>2952</v>
+        <v>2522</v>
       </c>
       <c r="I216" t="b">
         <v>0</v>
@@ -30951,7 +30921,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>2168</v>
+        <v>1758</v>
       </c>
       <c r="I217" t="b">
         <v>0</v>
@@ -31033,7 +31003,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="I218" t="b">
         <v>0</v>
@@ -31043,20 +31013,20 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L218" t="n">
         <v>26.44161851777137</v>
       </c>
       <c r="M218" t="n">
-        <v>26.44161851777137</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>26.44161851777137</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
-        <v>26.44161851777137</v>
+        <v>0</v>
       </c>
       <c r="P218" t="n">
         <v>0.0009926201174069952</v>
@@ -31065,16 +31035,16 @@
         <v>187625938.5589086</v>
       </c>
       <c r="R218" t="n">
-        <v>0.04134756817727944</v>
+        <v>0.02609735064488894</v>
       </c>
       <c r="S218" t="n">
-        <v>0.02502328957512319</v>
+        <v>0.01221104509309979</v>
       </c>
       <c r="T218" t="n">
-        <v>0.006809926575976191</v>
+        <v>0.003970518113058245</v>
       </c>
       <c r="U218" t="n">
-        <v>0.0707296932502913</v>
+        <v>0.03444019470800971</v>
       </c>
       <c r="V218" t="n">
         <v>30</v>
@@ -31115,7 +31085,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>1604</v>
+        <v>1316</v>
       </c>
       <c r="I219" t="b">
         <v>0</v>
@@ -31197,7 +31167,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>4164</v>
+        <v>3442</v>
       </c>
       <c r="I220" t="b">
         <v>0</v>
@@ -31279,7 +31249,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>1349</v>
+        <v>1172</v>
       </c>
       <c r="I221" t="b">
         <v>0</v>
@@ -31361,7 +31331,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>1231</v>
+        <v>1018</v>
       </c>
       <c r="I222" t="b">
         <v>0</v>
@@ -31443,7 +31413,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I223" t="b">
         <v>0</v>
@@ -31453,20 +31423,20 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L223" t="n">
         <v>1.072687171428666e-06</v>
       </c>
       <c r="M223" t="n">
-        <v>1.072687171428666e-06</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>1.072687171428666e-06</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
-        <v>1.072687171428666e-06</v>
+        <v>0</v>
       </c>
       <c r="P223" t="n">
         <v>0.0001667993863805342</v>
@@ -31475,16 +31445,16 @@
         <v>56181944.05622139</v>
       </c>
       <c r="R223" t="n">
-        <v>0.008804732243868013</v>
+        <v>0.008804732190531897</v>
       </c>
       <c r="S223" t="n">
-        <v>0.004761985771102762</v>
+        <v>0.004761985724977053</v>
       </c>
       <c r="T223" t="n">
-        <v>0.0005739513925912924</v>
+        <v>0.0005739513978878265</v>
       </c>
       <c r="U223" t="n">
-        <v>0.01356253691950002</v>
+        <v>0.01356253678684254</v>
       </c>
       <c r="V223" t="n">
         <v>30</v>
@@ -31525,7 +31495,7 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>855</v>
+        <v>710</v>
       </c>
       <c r="I224" t="b">
         <v>0</v>
@@ -31607,7 +31577,7 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>1595</v>
+        <v>1360</v>
       </c>
       <c r="I225" t="b">
         <v>0</v>
@@ -31689,7 +31659,7 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="I226" t="b">
         <v>0</v>
@@ -31771,7 +31741,7 @@
         </is>
       </c>
       <c r="H227" t="n">
-        <v>691</v>
+        <v>579</v>
       </c>
       <c r="I227" t="b">
         <v>0</v>
@@ -31853,21 +31823,21 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J228" t="b">
         <v>0</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>insufficient_signal</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L228" t="n">
-        <v>99.99999999992984</v>
+        <v>0</v>
       </c>
       <c r="M228" t="n">
         <v>0</v>
@@ -31933,7 +31903,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>515</v>
+        <v>433</v>
       </c>
       <c r="I229" t="b">
         <v>0</v>
@@ -32013,7 +31983,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>722</v>
+        <v>628</v>
       </c>
       <c r="I230" t="b">
         <v>0</v>
@@ -32093,7 +32063,7 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I231" t="b">
         <v>0</v>
@@ -32103,20 +32073,20 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L231" t="n">
         <v>0.0004117208146238172</v>
       </c>
       <c r="M231" t="n">
-        <v>0.0004117208146238172</v>
+        <v>0</v>
       </c>
       <c r="N231" t="n">
-        <v>0.0004117208146238172</v>
+        <v>0</v>
       </c>
       <c r="O231" t="n">
-        <v>0.0004117208146238172</v>
+        <v>0</v>
       </c>
       <c r="P231" t="n">
         <v>2.138326352655178e-05</v>
@@ -32125,16 +32095,16 @@
         <v>7135339.721805194</v>
       </c>
       <c r="R231" t="n">
-        <v>0.001748978019952733</v>
+        <v>0.001748977178015308</v>
       </c>
       <c r="S231" t="n">
-        <v>0.001032702465064047</v>
+        <v>0.001032701649405595</v>
       </c>
       <c r="T231" t="n">
-        <v>0.0001412297596008309</v>
+        <v>0.000141229139976861</v>
       </c>
       <c r="U231" t="n">
-        <v>0.002941733758162784</v>
+        <v>0.002941731457569461</v>
       </c>
       <c r="V231" t="n">
         <v>30</v>
@@ -32175,7 +32145,7 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>343</v>
+        <v>277</v>
       </c>
       <c r="I232" t="b">
         <v>0</v>
@@ -32255,7 +32225,7 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I233" t="b">
         <v>1</v>
@@ -32265,11 +32235,11 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>insufficient_signal</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L233" t="n">
-        <v>73.26228302528797</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
         <v>0</v>
@@ -32335,7 +32305,7 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="I234" t="b">
         <v>0</v>
@@ -32415,7 +32385,7 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="I235" t="b">
         <v>0</v>
@@ -32495,21 +32465,21 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I236" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J236" t="b">
         <v>0</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>insufficient_signal</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L236" t="n">
-        <v>99.99999999483958</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
         <v>0</v>
@@ -32575,7 +32545,7 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="I237" t="b">
         <v>0</v>
@@ -32654,11 +32624,9 @@
           <t>theta_estimation_windows</t>
         </is>
       </c>
-      <c r="H238" t="n">
-        <v>4</v>
-      </c>
+      <c r="H238" t="inlineStr"/>
       <c r="I238" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J238" t="b">
         <v>0</v>
@@ -32731,7 +32699,7 @@
         </is>
       </c>
       <c r="H239" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="I239" t="b">
         <v>0</v>
@@ -32811,7 +32779,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I240" t="b">
         <v>0</v>
@@ -32893,7 +32861,7 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I241" t="b">
         <v>1</v>
@@ -32903,11 +32871,11 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>insufficient_signal</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L241" t="n">
-        <v>99.99999982750137</v>
+        <v>0</v>
       </c>
       <c r="M241" t="n">
         <v>0</v>
@@ -32973,7 +32941,7 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="I242" t="b">
         <v>0</v>
@@ -32983,20 +32951,20 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_signal</t>
         </is>
       </c>
       <c r="L242" t="n">
         <v>0.0007096613591267564</v>
       </c>
       <c r="M242" t="n">
-        <v>0.0007096613591267564</v>
+        <v>0</v>
       </c>
       <c r="N242" t="n">
-        <v>0.0007096613591267564</v>
+        <v>0</v>
       </c>
       <c r="O242" t="n">
-        <v>0.0007096613591267564</v>
+        <v>0</v>
       </c>
       <c r="P242" t="n">
         <v>4.093369568507822e-06</v>
@@ -33005,16 +32973,16 @@
         <v>2107104.977566851</v>
       </c>
       <c r="R242" t="n">
-        <v>0.0001762164269127093</v>
+        <v>0.0001762164126836476</v>
       </c>
       <c r="S242" t="n">
-        <v>9.675119062532184e-05</v>
+        <v>9.675117789464187e-05</v>
       </c>
       <c r="T242" t="n">
-        <v>9.135287806773652e-06</v>
+        <v>9.135289224139579e-06</v>
       </c>
       <c r="U242" t="n">
-        <v>0.0002757831816405608</v>
+        <v>0.0002757831452863033</v>
       </c>
       <c r="V242" t="n">
         <v>30</v>
@@ -33054,11 +33022,9 @@
           <t>theta_estimation_windows</t>
         </is>
       </c>
-      <c r="H243" t="n">
-        <v>4</v>
-      </c>
+      <c r="H243" t="inlineStr"/>
       <c r="I243" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J243" t="b">
         <v>0</v>
@@ -33131,7 +33097,7 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I244" t="b">
         <v>0</v>
@@ -33211,7 +33177,7 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I245" t="b">
         <v>1</v>
@@ -33221,11 +33187,11 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>insufficient_deaths</t>
         </is>
       </c>
       <c r="L245" t="n">
-        <v>0.0003508892220213111</v>
+        <v>0</v>
       </c>
       <c r="M245" t="n">
         <v>0</v>
@@ -33239,9 +33205,7 @@
       <c r="P245" t="n">
         <v>4.517593406374983e-06</v>
       </c>
-      <c r="Q245" t="n">
-        <v>2779207.622979703</v>
-      </c>
+      <c r="Q245" t="inlineStr"/>
       <c r="R245" t="n">
         <v>0.0001523376942145475</v>
       </c>
@@ -33292,11 +33256,9 @@
           <t>theta_estimation_windows</t>
         </is>
       </c>
-      <c r="H246" t="n">
-        <v>2</v>
-      </c>
+      <c r="H246" t="inlineStr"/>
       <c r="I246" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J246" t="b">
         <v>0</v>
@@ -33350,10 +33312,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D247" t="n">
+        <v>-2</v>
       </c>
       <c r="E247" t="n">
         <v>0</v>
@@ -33369,7 +33329,7 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>10405</v>
+        <v>8321</v>
       </c>
       <c r="I247" t="b">
         <v>0</v>
@@ -33432,10 +33392,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D248" t="n">
+        <v>-2</v>
       </c>
       <c r="E248" t="n">
         <v>1</v>
@@ -33451,7 +33409,7 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>420</v>
+        <v>329</v>
       </c>
       <c r="I248" t="b">
         <v>0</v>
@@ -33514,10 +33472,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D249" t="n">
+        <v>-2</v>
       </c>
       <c r="E249" t="n">
         <v>2</v>
@@ -33533,7 +33489,7 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>7142</v>
+        <v>5817</v>
       </c>
       <c r="I249" t="b">
         <v>0</v>
@@ -33596,10 +33552,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D250" t="n">
+        <v>-2</v>
       </c>
       <c r="E250" t="n">
         <v>3</v>
@@ -33615,7 +33569,7 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>21869</v>
+        <v>17935</v>
       </c>
       <c r="I250" t="b">
         <v>0</v>
@@ -33678,10 +33632,8 @@
           <t>All Ages</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+      <c r="D251" t="n">
+        <v>-2</v>
       </c>
       <c r="E251" t="n">
         <v>4</v>
@@ -33697,7 +33649,7 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>8698</v>
+        <v>7333</v>
       </c>
       <c r="I251" t="b">
         <v>0</v>

--- a/data/Czech/KCOR_summary.xlsx
+++ b/data/Czech/KCOR_summary.xlsx
@@ -540,17 +540,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.2066</t>
+          <t>1.1567</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>1.132</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.233</t>
+          <t>1.182</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -581,17 +581,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.0161</t>
+          <t>0.9509</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>0.875</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.105</t>
+          <t>1.034</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -622,17 +622,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.0134</t>
+          <t>0.9581</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>0.920</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>0.998</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -663,17 +663,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.4317</t>
+          <t>1.3659</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.388</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.477</t>
+          <t>1.408</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -704,17 +704,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.4896</t>
+          <t>1.4484</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.377</t>
+          <t>1.339</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.612</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -745,17 +745,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.3231</t>
+          <t>1.2750</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.142</t>
+          <t>1.101</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.532</t>
+          <t>1.476</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -786,17 +786,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.9678</t>
+          <t>2.8393</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.330</t>
+          <t>2.230</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.780</t>
+          <t>3.616</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -827,17 +827,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.0879</t>
+          <t>1.0317</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>0.676</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.660</t>
+          <t>1.574</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -868,17 +868,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.3549</t>
+          <t>2.2365</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.402</t>
+          <t>1.334</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.954</t>
+          <t>3.751</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -909,17 +909,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12.6752</t>
+          <t>12.4845</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5.962</t>
+          <t>5.875</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26.946</t>
+          <t>26.530</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -984,17 +984,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.4421</t>
+          <t>1.3824</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.419</t>
+          <t>1.360</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.3571</t>
+          <t>1.2700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.297</t>
+          <t>1.216</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.420</t>
+          <t>1.327</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.4686</t>
+          <t>1.3886</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.506</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.4929</t>
+          <t>1.4243</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.437</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.480</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.2339</t>
+          <t>1.1997</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.151</t>
+          <t>1.119</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.323</t>
+          <t>1.286</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.2004</t>
+          <t>1.1567</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.038</t>
+          <t>1.001</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.388</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1230,17 +1230,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.0975</t>
+          <t>1.0500</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>0.827</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.334</t>
         </is>
       </c>
       <c r="F22" t="b">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.6309</t>
+          <t>0.5983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>0.924</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.2510</t>
+          <t>1.1881</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>0.709</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.099</t>
+          <t>1.991</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2.2822</t>
+          <t>2.2478</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.320</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16.279</t>
+          <t>16.031</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1962,17 +1962,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.1850</t>
+          <t>1.1305</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.162</t>
+          <t>1.109</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.208</t>
+          <t>1.152</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7970</t>
+          <t>0.7497</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.725</t>
+          <t>0.682</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>0.824</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -2044,17 +2044,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.0364</t>
+          <t>0.9737</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.985</t>
+          <t>0.926</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.090</t>
+          <t>1.024</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -2085,17 +2085,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.0937</t>
+          <t>1.0447</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>1.010</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>1.080</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.4863</t>
+          <t>1.4261</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.437</t>
+          <t>1.379</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -2167,17 +2167,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.4266</t>
+          <t>1.3663</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.342</t>
+          <t>1.286</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.516</t>
+          <t>1.451</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -2208,17 +2208,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.2429</t>
+          <t>1.1983</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.105</t>
+          <t>1.066</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1.347</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -2249,17 +2249,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.2066</t>
+          <t>1.1406</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>0.897</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.536</t>
+          <t>1.451</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.0902</t>
+          <t>1.0243</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.660</t>
+          <t>0.621</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.801</t>
+          <t>1.689</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -2331,17 +2331,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7.3475</t>
+          <t>7.2631</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.013</t>
+          <t>3.968</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13.454</t>
+          <t>13.294</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -2406,17 +2406,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.1262</t>
+          <t>1.0744</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.110</t>
+          <t>1.060</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.142</t>
+          <t>1.090</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -2447,17 +2447,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.0236</t>
+          <t>0.9628</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>0.922</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.070</t>
+          <t>1.005</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -2488,17 +2488,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.0691</t>
+          <t>1.0045</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.042</t>
+          <t>0.980</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.097</t>
+          <t>1.029</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -2529,17 +2529,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.2794</t>
+          <t>1.2221</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.247</t>
+          <t>1.192</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.313</t>
+          <t>1.253</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -2570,17 +2570,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.0898</t>
+          <t>1.0457</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.038</t>
+          <t>0.996</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.144</t>
+          <t>1.098</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.2368</t>
+          <t>1.1845</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.078</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>1.301</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.0287</t>
+          <t>0.9918</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>0.853</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.197</t>
+          <t>1.154</t>
         </is>
       </c>
       <c r="F22" t="b">
@@ -2693,17 +2693,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.7903</t>
+          <t>2.6376</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.181</t>
+          <t>2.064</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>3.371</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -2734,17 +2734,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.9048</t>
+          <t>0.8501</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>0.603</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.278</t>
+          <t>1.198</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -2775,17 +2775,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6.8041</t>
+          <t>6.7260</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>3.451</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13.267</t>
+          <t>13.110</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -3384,17 +3384,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.9902</t>
+          <t>0.9411</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.968</t>
+          <t>0.921</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>0.962</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7803</t>
+          <t>0.7375</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.655</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.880</t>
+          <t>0.831</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -3466,17 +3466,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.9529</t>
+          <t>0.8905</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>0.843</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>0.941</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -3507,17 +3507,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.9148</t>
+          <t>0.8708</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>0.834</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>0.909</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -3548,17 +3548,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.1362</t>
+          <t>1.0864</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.091</t>
+          <t>1.043</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.184</t>
+          <t>1.131</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -3589,17 +3589,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.1384</t>
+          <t>1.0885</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>1.027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.208</t>
+          <t>1.154</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.2451</t>
+          <t>1.1995</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.139</t>
+          <t>1.098</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.361</t>
+          <t>1.310</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.0103</t>
+          <t>0.9668</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>0.812</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.151</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -3712,17 +3712,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.4186</t>
+          <t>3.1828</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.435</t>
+          <t>2.274</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4.800</t>
+          <t>4.455</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -3753,17 +3753,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.5954</t>
+          <t>0.5841</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>0.300</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>1.135</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.0807</t>
+          <t>1.0271</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.066</t>
+          <t>1.014</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.095</t>
+          <t>1.041</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -3869,17 +3869,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.0309</t>
+          <t>0.9744</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>0.931</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.081</t>
+          <t>1.020</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -3910,17 +3910,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.0212</t>
+          <t>0.9543</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.995</t>
+          <t>0.931</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>0.978</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.1195</t>
+          <t>1.0657</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>1.040</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>1.092</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1.147</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -3992,17 +3992,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.3467</t>
+          <t>1.2876</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.301</t>
+          <t>1.245</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.394</t>
+          <t>1.332</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -4033,17 +4033,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.0854</t>
+          <t>1.0379</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.013</t>
+          <t>0.969</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.163</t>
+          <t>1.112</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -4074,17 +4074,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.1198</t>
+          <t>1.0787</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.964</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.253</t>
+          <t>1.207</t>
         </is>
       </c>
       <c r="F22" t="b">
@@ -4115,17 +4115,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.3660</t>
+          <t>1.3071</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.115</t>
+          <t>1.068</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.674</t>
+          <t>1.600</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.1371</t>
+          <t>1.9897</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.453</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.936</t>
+          <t>2.724</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -4197,17 +4197,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.9749</t>
+          <t>0.9564</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.586</t>
+          <t>0.575</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.622</t>
+          <t>1.590</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -4806,17 +4806,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.7436</t>
+          <t>0.7046</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>0.681</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>0.729</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -4847,17 +4847,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.5278</t>
+          <t>0.4983</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>0.413</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>0.601</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -4888,17 +4888,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.7267</t>
+          <t>0.6796</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>0.630</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.785</t>
+          <t>0.733</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -4929,17 +4929,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.6172</t>
+          <t>0.5852</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>0.544</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.665</t>
+          <t>0.630</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -4970,17 +4970,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.6433</t>
+          <t>0.6148</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>0.569</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>0.665</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -5011,17 +5011,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.9728</t>
+          <t>0.9279</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>0.831</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.086</t>
+          <t>1.036</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -5052,17 +5052,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.0787</t>
+          <t>1.0309</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.931</t>
+          <t>0.891</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>1.193</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -5093,17 +5093,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.2307</t>
+          <t>1.1718</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>0.952</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.516</t>
+          <t>1.442</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -5134,17 +5134,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.0784</t>
+          <t>1.0149</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>0.742</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.480</t>
+          <t>1.388</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -5175,17 +5175,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.2371</t>
+          <t>1.1818</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>0.803</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>1.738</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -5250,17 +5250,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.9653</t>
+          <t>0.9146</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>0.903</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>0.926</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -5291,17 +5291,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.9364</t>
+          <t>0.8840</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>0.844</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.982</t>
+          <t>0.926</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -5332,17 +5332,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.9062</t>
+          <t>0.8475</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>0.826</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.930</t>
+          <t>0.869</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -5373,17 +5373,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.9785</t>
+          <t>0.9278</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.955</t>
+          <t>0.906</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.003</t>
+          <t>0.950</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -5414,17 +5414,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.9889</t>
+          <t>0.9452</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.959</t>
+          <t>0.917</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.020</t>
+          <t>0.974</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -5455,17 +5455,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.2945</t>
+          <t>1.2347</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.232</t>
+          <t>1.176</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.360</t>
+          <t>1.296</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -5496,17 +5496,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.1196</t>
+          <t>1.0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.037</t>
+          <t>0.992</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.209</t>
+          <t>1.154</t>
         </is>
       </c>
       <c r="F22" t="b">
@@ -5537,17 +5537,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.7405</t>
+          <t>1.6572</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.507</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.910</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -5578,17 +5578,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.1971</t>
+          <t>1.1265</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>0.886</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.433</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -5619,17 +5619,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.2749</t>
+          <t>0.2626</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.157</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>0.440</t>
         </is>
       </c>
       <c r="F25" t="b">

--- a/data/Czech/KCOR_summary.xlsx
+++ b/data/Czech/KCOR_summary.xlsx
@@ -581,17 +581,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.9509</t>
+          <t>0.9563</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.879</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.034</t>
+          <t>1.040</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -622,17 +622,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.9581</t>
+          <t>0.9675</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.920</t>
+          <t>0.929</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.998</t>
+          <t>1.008</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -663,17 +663,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.3659</t>
+          <t>1.3752</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.334</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.408</t>
+          <t>1.418</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -704,17 +704,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.4484</t>
+          <t>1.4619</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.339</t>
+          <t>1.351</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -745,17 +745,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.2750</t>
+          <t>1.2838</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.101</t>
+          <t>1.109</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>1.487</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -786,17 +786,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.8393</t>
+          <t>2.8803</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.230</t>
+          <t>2.262</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.616</t>
+          <t>3.668</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -868,7 +868,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.2365</t>
+          <t>2.2377</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.751</t>
+          <t>3.753</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -909,7 +909,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12.4845</t>
+          <t>12.4847</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.2700</t>
+          <t>1.2787</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.216</t>
+          <t>1.224</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.327</t>
+          <t>1.336</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.3886</t>
+          <t>1.4037</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.369</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.439</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.4243</t>
+          <t>1.4339</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.380</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.480</t>
+          <t>1.490</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.1997</t>
+          <t>1.1758</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.119</t>
+          <t>1.094</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.263</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.1567</t>
+          <t>1.1614</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.001</t>
+          <t>1.004</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>1.343</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1230,17 +1230,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.0500</t>
+          <t>1.0652</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>0.838</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>1.353</t>
         </is>
       </c>
       <c r="F22" t="b">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.1881</t>
+          <t>1.1887</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.991</t>
+          <t>1.992</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2.2478</t>
+          <t>2.2479</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16.031</t>
+          <t>16.032</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1469,17 +1469,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.3356</t>
+          <t>1.3372</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>1.227</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -1510,17 +1510,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.4492</t>
+          <t>1.4509</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.389</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.512</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.8283</t>
+          <t>0.8042</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.747</t>
+          <t>0.724</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.918</t>
+          <t>0.893</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -1633,17 +1633,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.9072</t>
+          <t>0.9047</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.740</t>
+          <t>0.738</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.112</t>
+          <t>1.109</t>
         </is>
       </c>
       <c r="F33" t="b">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7497</t>
+          <t>0.7542</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>0.686</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>0.829</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -2044,17 +2044,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.9737</t>
+          <t>0.9887</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.926</t>
+          <t>0.940</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>1.040</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -2085,17 +2085,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.0447</t>
+          <t>1.0755</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.010</t>
+          <t>1.040</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.080</t>
+          <t>1.112</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.4261</t>
+          <t>1.4794</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.379</t>
+          <t>1.430</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.530</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -2167,17 +2167,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.3663</t>
+          <t>1.4182</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>1.507</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -2208,17 +2208,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.1983</t>
+          <t>1.2390</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.066</t>
+          <t>1.102</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.347</t>
+          <t>1.393</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -2249,17 +2249,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.1406</t>
+          <t>1.1591</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>0.911</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.0243</t>
+          <t>1.0244</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.689</t>
+          <t>1.690</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7.2631</t>
+          <t>7.2633</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2447,17 +2447,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.9628</t>
+          <t>0.9696</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.922</t>
+          <t>0.928</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.005</t>
+          <t>1.013</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -2488,17 +2488,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.0045</t>
+          <t>1.0199</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.980</t>
+          <t>0.995</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.029</t>
+          <t>1.045</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -2529,17 +2529,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.2221</t>
+          <t>1.2582</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.192</t>
+          <t>1.226</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.253</t>
+          <t>1.291</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -2570,17 +2570,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.0457</t>
+          <t>1.0602</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.996</t>
+          <t>1.009</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.098</t>
+          <t>1.114</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.1845</t>
+          <t>1.2295</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>1.119</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.301</t>
+          <t>1.351</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.9918</t>
+          <t>1.0255</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>0.881</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.154</t>
+          <t>1.193</t>
         </is>
       </c>
       <c r="F22" t="b">
@@ -2693,17 +2693,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.6376</t>
+          <t>2.6803</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.064</t>
+          <t>2.097</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3.371</t>
+          <t>3.427</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.8501</t>
+          <t>0.8502</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6.7260</t>
+          <t>6.7262</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13.110</t>
+          <t>13.111</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.2843</t>
+          <t>1.2856</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.169</t>
+          <t>1.170</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.411</t>
+          <t>1.413</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -3014,17 +3014,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.7332</t>
+          <t>0.7166</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>0.679</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>0.757</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -3466,17 +3466,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.8905</t>
+          <t>0.9019</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.843</t>
+          <t>0.853</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.941</t>
+          <t>0.953</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -3507,17 +3507,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.8708</t>
+          <t>0.9000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>0.862</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>0.940</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -3548,17 +3548,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.0864</t>
+          <t>1.1401</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.043</t>
+          <t>1.094</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>1.188</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -3589,17 +3589,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.0885</t>
+          <t>1.1413</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>1.076</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.154</t>
+          <t>1.211</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.1995</t>
+          <t>1.2440</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.098</t>
+          <t>1.138</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.310</t>
+          <t>1.360</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.135</t>
+          <t>1.136</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -3910,17 +3910,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.9543</t>
+          <t>0.9696</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.931</t>
+          <t>0.946</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>0.994</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.0657</t>
+          <t>1.1030</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.040</t>
+          <t>1.076</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.092</t>
+          <t>1.130</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -3992,17 +3992,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.2876</t>
+          <t>1.3513</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.245</t>
+          <t>1.306</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.332</t>
+          <t>1.399</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -4033,17 +4033,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.0379</t>
+          <t>1.0883</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>1.016</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.112</t>
+          <t>1.166</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -4074,17 +4074,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.0787</t>
+          <t>1.1188</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.964</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.207</t>
+          <t>1.252</t>
         </is>
       </c>
       <c r="F22" t="b">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.9564</t>
+          <t>0.9565</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4354,17 +4354,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.0717</t>
+          <t>1.0751</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.015</t>
+          <t>1.018</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.132</t>
+          <t>1.135</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -4395,17 +4395,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.2238</t>
+          <t>1.2256</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.172</t>
+          <t>1.173</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.278</t>
+          <t>1.280</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -4888,17 +4888,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.6796</t>
+          <t>0.6861</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.630</t>
+          <t>0.636</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>0.741</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -4929,17 +4929,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.5852</t>
+          <t>0.6071</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>0.564</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.630</t>
+          <t>0.654</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -4970,17 +4970,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.6148</t>
+          <t>0.6494</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>0.601</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.665</t>
+          <t>0.702</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -5011,17 +5011,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.9279</t>
+          <t>0.9741</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.831</t>
+          <t>0.872</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.036</t>
+          <t>1.088</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -5052,17 +5052,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.0309</t>
+          <t>1.0766</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>0.929</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1.247</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -5332,17 +5332,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.8475</t>
+          <t>0.8582</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>0.837</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.869</t>
+          <t>0.880</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -5373,17 +5373,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.9278</t>
+          <t>0.9625</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.906</t>
+          <t>0.940</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.950</t>
+          <t>0.986</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -5414,17 +5414,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.9452</t>
+          <t>0.9983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.917</t>
+          <t>0.968</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>1.030</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -5455,17 +5455,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.2347</t>
+          <t>1.2962</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.176</t>
+          <t>1.233</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.296</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -5496,17 +5496,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.0700</t>
+          <t>1.1174</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.992</t>
+          <t>1.035</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.154</t>
+          <t>1.206</t>
         </is>
       </c>
       <c r="F22" t="b">
@@ -5776,17 +5776,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.2471</t>
+          <t>1.2509</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.157</t>
+          <t>1.160</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1.349</t>
         </is>
       </c>
       <c r="F30" t="b">
